--- a/AC_2010Bye/AC_029_Sircilla.xlsx
+++ b/AC_2010Bye/AC_029_Sircilla.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,14 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +65,26 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -82,11 +106,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -102,6 +168,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF229"/>
+  <dimension ref="A1:CF231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -578,6 +657,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -58093,333 +58173,928 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="6" t="inlineStr">
+      <c r="A229" s="8" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="C229" s="7">
+      <c r="B229" s="13" t="inlineStr"/>
+      <c r="C229" s="14">
         <f>SUM(C6:C228)</f>
         <v/>
       </c>
-      <c r="D229" s="7">
+      <c r="D229" s="14">
         <f>SUM(D6:D228)</f>
         <v/>
       </c>
-      <c r="E229" s="7">
+      <c r="E229" s="14">
         <f>SUM(E6:E228)</f>
         <v/>
       </c>
-      <c r="F229" s="7">
+      <c r="F229" s="14">
         <f>SUM(F6:F228)</f>
         <v/>
       </c>
-      <c r="G229" s="7">
+      <c r="G229" s="14">
         <f>SUM(G6:G228)</f>
         <v/>
       </c>
-      <c r="H229" s="7">
+      <c r="H229" s="14">
         <f>SUM(H6:H228)</f>
         <v/>
       </c>
-      <c r="I229" s="7">
+      <c r="I229" s="14">
         <f>SUM(I6:I228)</f>
         <v/>
       </c>
-      <c r="J229" s="7">
+      <c r="J229" s="14">
         <f>SUM(J6:J228)</f>
         <v/>
       </c>
-      <c r="K229" s="7">
+      <c r="K229" s="14">
         <f>SUM(K6:K228)</f>
         <v/>
       </c>
-      <c r="L229" s="7">
+      <c r="L229" s="14">
         <f>SUM(L6:L228)</f>
         <v/>
       </c>
-      <c r="M229" s="7">
+      <c r="M229" s="14">
         <f>SUM(M6:M228)</f>
         <v/>
       </c>
-      <c r="N229" s="7">
+      <c r="N229" s="14">
         <f>SUM(N6:N228)</f>
         <v/>
       </c>
-      <c r="O229" s="7">
+      <c r="O229" s="14">
         <f>SUM(O6:O228)</f>
         <v/>
       </c>
-      <c r="P229" s="7">
+      <c r="P229" s="14">
         <f>SUM(P6:P228)</f>
         <v/>
       </c>
-      <c r="Q229" s="7">
+      <c r="Q229" s="14">
         <f>SUM(Q6:Q228)</f>
         <v/>
       </c>
-      <c r="R229" s="7">
+      <c r="R229" s="14">
         <f>SUM(R6:R228)</f>
         <v/>
       </c>
-      <c r="S229" s="7">
+      <c r="S229" s="14">
         <f>SUM(S6:S228)</f>
         <v/>
       </c>
-      <c r="T229" s="7">
+      <c r="T229" s="14">
         <f>SUM(T6:T228)</f>
         <v/>
       </c>
-      <c r="U229" s="7">
+      <c r="U229" s="14">
         <f>SUM(U6:U228)</f>
         <v/>
       </c>
-      <c r="V229" s="7">
+      <c r="V229" s="14">
         <f>SUM(V6:V228)</f>
         <v/>
       </c>
-      <c r="W229" s="7">
+      <c r="W229" s="14">
         <f>SUM(W6:W228)</f>
         <v/>
       </c>
-      <c r="X229" s="7">
+      <c r="X229" s="14">
         <f>SUM(X6:X228)</f>
         <v/>
       </c>
-      <c r="Y229" s="7">
+      <c r="Y229" s="14">
         <f>SUM(Y6:Y228)</f>
         <v/>
       </c>
-      <c r="Z229" s="7">
+      <c r="Z229" s="14">
         <f>SUM(Z6:Z228)</f>
         <v/>
       </c>
-      <c r="AA229" s="7">
+      <c r="AA229" s="14">
         <f>SUM(AA6:AA228)</f>
         <v/>
       </c>
-      <c r="AB229" s="7">
+      <c r="AB229" s="14">
         <f>SUM(AB6:AB228)</f>
         <v/>
       </c>
-      <c r="AC229" s="7">
+      <c r="AC229" s="14">
         <f>SUM(AC6:AC228)</f>
         <v/>
       </c>
-      <c r="AD229" s="7">
+      <c r="AD229" s="14">
         <f>SUM(AD6:AD228)</f>
         <v/>
       </c>
-      <c r="AE229" s="7">
+      <c r="AE229" s="14">
         <f>SUM(AE6:AE228)</f>
         <v/>
       </c>
-      <c r="AF229" s="7">
+      <c r="AF229" s="14">
         <f>SUM(AF6:AF228)</f>
         <v/>
       </c>
-      <c r="AG229" s="7">
+      <c r="AG229" s="14">
         <f>SUM(AG6:AG228)</f>
         <v/>
       </c>
-      <c r="AH229" s="7">
+      <c r="AH229" s="14">
         <f>SUM(AH6:AH228)</f>
         <v/>
       </c>
-      <c r="AI229" s="7">
+      <c r="AI229" s="14">
         <f>SUM(AI6:AI228)</f>
         <v/>
       </c>
-      <c r="AJ229" s="7">
+      <c r="AJ229" s="14">
         <f>SUM(AJ6:AJ228)</f>
         <v/>
       </c>
-      <c r="AK229" s="7">
+      <c r="AK229" s="14">
         <f>SUM(AK6:AK228)</f>
         <v/>
       </c>
-      <c r="AL229" s="7">
+      <c r="AL229" s="14">
         <f>SUM(AL6:AL228)</f>
         <v/>
       </c>
-      <c r="AM229" s="7">
+      <c r="AM229" s="14">
         <f>SUM(AM6:AM228)</f>
         <v/>
       </c>
-      <c r="AN229" s="7">
+      <c r="AN229" s="14">
         <f>SUM(AN6:AN228)</f>
         <v/>
       </c>
-      <c r="AO229" s="7">
+      <c r="AO229" s="14">
         <f>SUM(AO6:AO228)</f>
         <v/>
       </c>
-      <c r="AP229" s="7">
+      <c r="AP229" s="14">
         <f>SUM(AP6:AP228)</f>
         <v/>
       </c>
-      <c r="AQ229" s="7">
+      <c r="AQ229" s="14">
         <f>SUM(AQ6:AQ228)</f>
         <v/>
       </c>
-      <c r="AR229" s="7">
+      <c r="AR229" s="14">
         <f>SUM(AR6:AR228)</f>
         <v/>
       </c>
-      <c r="AS229" s="7">
+      <c r="AS229" s="14">
         <f>SUM(AS6:AS228)</f>
         <v/>
       </c>
-      <c r="AT229" s="7">
+      <c r="AT229" s="14">
         <f>SUM(AT6:AT228)</f>
         <v/>
       </c>
-      <c r="AU229" s="7">
+      <c r="AU229" s="14">
         <f>SUM(AU6:AU228)</f>
         <v/>
       </c>
-      <c r="AV229" s="7">
+      <c r="AV229" s="14">
         <f>SUM(AV6:AV228)</f>
         <v/>
       </c>
-      <c r="AW229" s="7">
+      <c r="AW229" s="14">
         <f>SUM(AW6:AW228)</f>
         <v/>
       </c>
-      <c r="AX229" s="7">
+      <c r="AX229" s="14">
         <f>SUM(AX6:AX228)</f>
         <v/>
       </c>
-      <c r="AY229" s="7">
+      <c r="AY229" s="14">
         <f>SUM(AY6:AY228)</f>
         <v/>
       </c>
-      <c r="AZ229" s="7">
+      <c r="AZ229" s="14">
         <f>SUM(AZ6:AZ228)</f>
         <v/>
       </c>
-      <c r="BA229" s="7">
+      <c r="BA229" s="14">
         <f>SUM(BA6:BA228)</f>
         <v/>
       </c>
-      <c r="BB229" s="7">
+      <c r="BB229" s="14">
         <f>SUM(BB6:BB228)</f>
         <v/>
       </c>
-      <c r="BC229" s="7">
+      <c r="BC229" s="14">
         <f>SUM(BC6:BC228)</f>
         <v/>
       </c>
-      <c r="BD229" s="7">
+      <c r="BD229" s="14">
         <f>SUM(BD6:BD228)</f>
         <v/>
       </c>
-      <c r="BE229" s="7">
+      <c r="BE229" s="14">
         <f>SUM(BE6:BE228)</f>
         <v/>
       </c>
-      <c r="BF229" s="7">
+      <c r="BF229" s="14">
         <f>SUM(BF6:BF228)</f>
         <v/>
       </c>
-      <c r="BG229" s="7">
+      <c r="BG229" s="14">
         <f>SUM(BG6:BG228)</f>
         <v/>
       </c>
-      <c r="BH229" s="7">
+      <c r="BH229" s="14">
         <f>SUM(BH6:BH228)</f>
         <v/>
       </c>
-      <c r="BI229" s="7">
+      <c r="BI229" s="14">
         <f>SUM(BI6:BI228)</f>
         <v/>
       </c>
-      <c r="BJ229" s="7">
+      <c r="BJ229" s="14">
         <f>SUM(BJ6:BJ228)</f>
         <v/>
       </c>
-      <c r="BK229" s="7">
+      <c r="BK229" s="14">
         <f>SUM(BK6:BK228)</f>
         <v/>
       </c>
-      <c r="BL229" s="7">
+      <c r="BL229" s="14">
         <f>SUM(BL6:BL228)</f>
         <v/>
       </c>
-      <c r="BM229" s="7">
+      <c r="BM229" s="14">
         <f>SUM(BM6:BM228)</f>
         <v/>
       </c>
-      <c r="BN229" s="7">
+      <c r="BN229" s="14">
         <f>SUM(BN6:BN228)</f>
         <v/>
       </c>
-      <c r="BO229" s="7">
+      <c r="BO229" s="14">
         <f>SUM(BO6:BO228)</f>
         <v/>
       </c>
-      <c r="BP229" s="7">
+      <c r="BP229" s="14">
         <f>SUM(BP6:BP228)</f>
         <v/>
       </c>
-      <c r="BQ229" s="7">
+      <c r="BQ229" s="14">
         <f>SUM(BQ6:BQ228)</f>
         <v/>
       </c>
-      <c r="BR229" s="7">
+      <c r="BR229" s="14">
         <f>SUM(BR6:BR228)</f>
         <v/>
       </c>
-      <c r="BS229" s="7">
+      <c r="BS229" s="14">
         <f>SUM(BS6:BS228)</f>
         <v/>
       </c>
-      <c r="BT229" s="7">
+      <c r="BT229" s="14">
         <f>SUM(BT6:BT228)</f>
         <v/>
       </c>
-      <c r="BU229" s="7">
+      <c r="BU229" s="14">
         <f>SUM(BU6:BU228)</f>
         <v/>
       </c>
-      <c r="BV229" s="7">
+      <c r="BV229" s="14">
         <f>SUM(BV6:BV228)</f>
         <v/>
       </c>
-      <c r="BW229" s="7">
+      <c r="BW229" s="14">
         <f>SUM(BW6:BW228)</f>
         <v/>
       </c>
-      <c r="BX229" s="7">
+      <c r="BX229" s="14">
         <f>SUM(BX6:BX228)</f>
         <v/>
       </c>
-      <c r="BY229" s="7">
+      <c r="BY229" s="14">
         <f>SUM(BY6:BY228)</f>
         <v/>
       </c>
-      <c r="BZ229" s="7">
+      <c r="BZ229" s="14">
         <f>SUM(BZ6:BZ228)</f>
         <v/>
       </c>
-      <c r="CA229" s="7">
+      <c r="CA229" s="14">
         <f>SUM(CA6:CA228)</f>
         <v/>
       </c>
-      <c r="CB229" s="7">
+      <c r="CB229" s="14">
         <f>SUM(CB6:CB228)</f>
         <v/>
       </c>
-      <c r="CC229" s="7">
+      <c r="CC229" s="14">
         <f>SUM(CC6:CC228)</f>
         <v/>
       </c>
-      <c r="CD229" s="7">
+      <c r="CD229" s="14">
         <f>SUM(CD6:CD228)</f>
         <v/>
       </c>
-      <c r="CE229" s="7">
+      <c r="CE229" s="14">
         <f>SUM(CE6:CE228)</f>
+        <v/>
+      </c>
+      <c r="CF229" s="14">
+        <f>SUM(CF6:CF228)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="9" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="B230" s="10" t="inlineStr"/>
+      <c r="C230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB230" s="10" t="n">
+        <v>268</v>
+      </c>
+      <c r="CC230" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="CD230" s="10" t="n">
+        <v>325</v>
+      </c>
+      <c r="CE230" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF230" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="B231" s="12" t="inlineStr"/>
+      <c r="C231" s="12">
+        <f>C229+C230</f>
+        <v/>
+      </c>
+      <c r="D231" s="12">
+        <f>D229+D230</f>
+        <v/>
+      </c>
+      <c r="E231" s="12">
+        <f>E229+E230</f>
+        <v/>
+      </c>
+      <c r="F231" s="12">
+        <f>F229+F230</f>
+        <v/>
+      </c>
+      <c r="G231" s="12">
+        <f>G229+G230</f>
+        <v/>
+      </c>
+      <c r="H231" s="12">
+        <f>H229+H230</f>
+        <v/>
+      </c>
+      <c r="I231" s="12">
+        <f>I229+I230</f>
+        <v/>
+      </c>
+      <c r="J231" s="12">
+        <f>J229+J230</f>
+        <v/>
+      </c>
+      <c r="K231" s="12">
+        <f>K229+K230</f>
+        <v/>
+      </c>
+      <c r="L231" s="12">
+        <f>L229+L230</f>
+        <v/>
+      </c>
+      <c r="M231" s="12">
+        <f>M229+M230</f>
+        <v/>
+      </c>
+      <c r="N231" s="12">
+        <f>N229+N230</f>
+        <v/>
+      </c>
+      <c r="O231" s="12">
+        <f>O229+O230</f>
+        <v/>
+      </c>
+      <c r="P231" s="12">
+        <f>P229+P230</f>
+        <v/>
+      </c>
+      <c r="Q231" s="12">
+        <f>Q229+Q230</f>
+        <v/>
+      </c>
+      <c r="R231" s="12">
+        <f>R229+R230</f>
+        <v/>
+      </c>
+      <c r="S231" s="12">
+        <f>S229+S230</f>
+        <v/>
+      </c>
+      <c r="T231" s="12">
+        <f>T229+T230</f>
+        <v/>
+      </c>
+      <c r="U231" s="12">
+        <f>U229+U230</f>
+        <v/>
+      </c>
+      <c r="V231" s="12">
+        <f>V229+V230</f>
+        <v/>
+      </c>
+      <c r="W231" s="12">
+        <f>W229+W230</f>
+        <v/>
+      </c>
+      <c r="X231" s="12">
+        <f>X229+X230</f>
+        <v/>
+      </c>
+      <c r="Y231" s="12">
+        <f>Y229+Y230</f>
+        <v/>
+      </c>
+      <c r="Z231" s="12">
+        <f>Z229+Z230</f>
+        <v/>
+      </c>
+      <c r="AA231" s="12">
+        <f>AA229+AA230</f>
+        <v/>
+      </c>
+      <c r="AB231" s="12">
+        <f>AB229+AB230</f>
+        <v/>
+      </c>
+      <c r="AC231" s="12">
+        <f>AC229+AC230</f>
+        <v/>
+      </c>
+      <c r="AD231" s="12">
+        <f>AD229+AD230</f>
+        <v/>
+      </c>
+      <c r="AE231" s="12">
+        <f>AE229+AE230</f>
+        <v/>
+      </c>
+      <c r="AF231" s="12">
+        <f>AF229+AF230</f>
+        <v/>
+      </c>
+      <c r="AG231" s="12">
+        <f>AG229+AG230</f>
+        <v/>
+      </c>
+      <c r="AH231" s="12">
+        <f>AH229+AH230</f>
+        <v/>
+      </c>
+      <c r="AI231" s="12">
+        <f>AI229+AI230</f>
+        <v/>
+      </c>
+      <c r="AJ231" s="12">
+        <f>AJ229+AJ230</f>
+        <v/>
+      </c>
+      <c r="AK231" s="12">
+        <f>AK229+AK230</f>
+        <v/>
+      </c>
+      <c r="AL231" s="12">
+        <f>AL229+AL230</f>
+        <v/>
+      </c>
+      <c r="AM231" s="12">
+        <f>AM229+AM230</f>
+        <v/>
+      </c>
+      <c r="AN231" s="12">
+        <f>AN229+AN230</f>
+        <v/>
+      </c>
+      <c r="AO231" s="12">
+        <f>AO229+AO230</f>
+        <v/>
+      </c>
+      <c r="AP231" s="12">
+        <f>AP229+AP230</f>
+        <v/>
+      </c>
+      <c r="AQ231" s="12">
+        <f>AQ229+AQ230</f>
+        <v/>
+      </c>
+      <c r="AR231" s="12">
+        <f>AR229+AR230</f>
+        <v/>
+      </c>
+      <c r="AS231" s="12">
+        <f>AS229+AS230</f>
+        <v/>
+      </c>
+      <c r="AT231" s="12">
+        <f>AT229+AT230</f>
+        <v/>
+      </c>
+      <c r="AU231" s="12">
+        <f>AU229+AU230</f>
+        <v/>
+      </c>
+      <c r="AV231" s="12">
+        <f>AV229+AV230</f>
+        <v/>
+      </c>
+      <c r="AW231" s="12">
+        <f>AW229+AW230</f>
+        <v/>
+      </c>
+      <c r="AX231" s="12">
+        <f>AX229+AX230</f>
+        <v/>
+      </c>
+      <c r="AY231" s="12">
+        <f>AY229+AY230</f>
+        <v/>
+      </c>
+      <c r="AZ231" s="12">
+        <f>AZ229+AZ230</f>
+        <v/>
+      </c>
+      <c r="BA231" s="12">
+        <f>BA229+BA230</f>
+        <v/>
+      </c>
+      <c r="BB231" s="12">
+        <f>BB229+BB230</f>
+        <v/>
+      </c>
+      <c r="BC231" s="12">
+        <f>BC229+BC230</f>
+        <v/>
+      </c>
+      <c r="BD231" s="12">
+        <f>BD229+BD230</f>
+        <v/>
+      </c>
+      <c r="BE231" s="12">
+        <f>BE229+BE230</f>
+        <v/>
+      </c>
+      <c r="BF231" s="12">
+        <f>BF229+BF230</f>
+        <v/>
+      </c>
+      <c r="BG231" s="12">
+        <f>BG229+BG230</f>
+        <v/>
+      </c>
+      <c r="BH231" s="12">
+        <f>BH229+BH230</f>
+        <v/>
+      </c>
+      <c r="BI231" s="12">
+        <f>BI229+BI230</f>
+        <v/>
+      </c>
+      <c r="BJ231" s="12">
+        <f>BJ229+BJ230</f>
+        <v/>
+      </c>
+      <c r="BK231" s="12">
+        <f>BK229+BK230</f>
+        <v/>
+      </c>
+      <c r="BL231" s="12">
+        <f>BL229+BL230</f>
+        <v/>
+      </c>
+      <c r="BM231" s="12">
+        <f>BM229+BM230</f>
+        <v/>
+      </c>
+      <c r="BN231" s="12">
+        <f>BN229+BN230</f>
+        <v/>
+      </c>
+      <c r="BO231" s="12">
+        <f>BO229+BO230</f>
+        <v/>
+      </c>
+      <c r="BP231" s="12">
+        <f>BP229+BP230</f>
+        <v/>
+      </c>
+      <c r="BQ231" s="12">
+        <f>BQ229+BQ230</f>
+        <v/>
+      </c>
+      <c r="BR231" s="12">
+        <f>BR229+BR230</f>
+        <v/>
+      </c>
+      <c r="BS231" s="12">
+        <f>BS229+BS230</f>
+        <v/>
+      </c>
+      <c r="BT231" s="12">
+        <f>BT229+BT230</f>
+        <v/>
+      </c>
+      <c r="BU231" s="12">
+        <f>BU229+BU230</f>
+        <v/>
+      </c>
+      <c r="BV231" s="12">
+        <f>BV229+BV230</f>
+        <v/>
+      </c>
+      <c r="BW231" s="12">
+        <f>BW229+BW230</f>
+        <v/>
+      </c>
+      <c r="BX231" s="12">
+        <f>BX229+BX230</f>
+        <v/>
+      </c>
+      <c r="BY231" s="12">
+        <f>BY229+BY230</f>
+        <v/>
+      </c>
+      <c r="BZ231" s="12">
+        <f>BZ229+BZ230</f>
+        <v/>
+      </c>
+      <c r="CA231" s="12">
+        <f>CA229+CA230</f>
+        <v/>
+      </c>
+      <c r="CB231" s="12">
+        <f>CB229+CB230</f>
+        <v/>
+      </c>
+      <c r="CC231" s="12">
+        <f>CC229+CC230</f>
+        <v/>
+      </c>
+      <c r="CD231" s="12">
+        <f>CD229+CD230</f>
+        <v/>
+      </c>
+      <c r="CE231" s="12">
+        <f>CE229+CE230</f>
+        <v/>
+      </c>
+      <c r="CF231" s="12">
+        <f>CF229+CF230</f>
         <v/>
       </c>
     </row>

--- a/AC_2010Bye/AC_029_Sircilla.xlsx
+++ b/AC_2010Bye/AC_029_Sircilla.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -84,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -148,11 +153,19 @@
         <color rgb="001B365D"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -180,6 +193,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -657,7 +689,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -1321,13 +1352,13 @@
         <v>0</v>
       </c>
       <c r="CB6" s="4" t="n">
-        <v>703</v>
+        <v>655</v>
       </c>
       <c r="CC6" s="4" t="n">
         <v>29</v>
       </c>
       <c r="CD6" s="4" t="n">
-        <v>732</v>
+        <v>684</v>
       </c>
       <c r="CE6" s="4" t="n">
         <v>0</v>
@@ -1577,13 +1608,13 @@
         <v>0</v>
       </c>
       <c r="CB7" s="4" t="n">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="CC7" s="4" t="n">
         <v>19</v>
       </c>
       <c r="CD7" s="4" t="n">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="CE7" s="4" t="n">
         <v>0</v>
@@ -1833,13 +1864,13 @@
         <v>0</v>
       </c>
       <c r="CB8" s="4" t="n">
-        <v>661</v>
+        <v>643</v>
       </c>
       <c r="CC8" s="4" t="n">
         <v>27</v>
       </c>
       <c r="CD8" s="4" t="n">
-        <v>688</v>
+        <v>670</v>
       </c>
       <c r="CE8" s="4" t="n">
         <v>0</v>
@@ -2345,13 +2376,13 @@
         <v>0</v>
       </c>
       <c r="CB10" s="4" t="n">
-        <v>713</v>
+        <v>693</v>
       </c>
       <c r="CC10" s="4" t="n">
         <v>31</v>
       </c>
       <c r="CD10" s="4" t="n">
-        <v>744</v>
+        <v>724</v>
       </c>
       <c r="CE10" s="4" t="n">
         <v>0</v>
@@ -2601,13 +2632,13 @@
         <v>2</v>
       </c>
       <c r="CB11" s="4" t="n">
-        <v>891</v>
+        <v>866</v>
       </c>
       <c r="CC11" s="4" t="n">
         <v>30</v>
       </c>
       <c r="CD11" s="4" t="n">
-        <v>921</v>
+        <v>896</v>
       </c>
       <c r="CE11" s="4" t="n">
         <v>0</v>
@@ -2857,13 +2888,13 @@
         <v>0</v>
       </c>
       <c r="CB12" s="4" t="n">
-        <v>743</v>
+        <v>719</v>
       </c>
       <c r="CC12" s="4" t="n">
         <v>23</v>
       </c>
       <c r="CD12" s="4" t="n">
-        <v>766</v>
+        <v>742</v>
       </c>
       <c r="CE12" s="4" t="n">
         <v>0</v>
@@ -3113,13 +3144,13 @@
         <v>1</v>
       </c>
       <c r="CB13" s="4" t="n">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="CC13" s="4" t="n">
         <v>15</v>
       </c>
       <c r="CD13" s="4" t="n">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="CE13" s="4" t="n">
         <v>0</v>
@@ -3370,13 +3401,13 @@
         <v>0</v>
       </c>
       <c r="CB14" s="4" t="n">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="CC14" s="4" t="n">
         <v>17</v>
       </c>
       <c r="CD14" s="4" t="n">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="CE14" s="4" t="n">
         <v>0</v>
@@ -3626,13 +3657,13 @@
         <v>0</v>
       </c>
       <c r="CB15" s="4" t="n">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="CC15" s="4" t="n">
         <v>15</v>
       </c>
       <c r="CD15" s="4" t="n">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="CE15" s="4" t="n">
         <v>0</v>
@@ -3882,13 +3913,13 @@
         <v>0</v>
       </c>
       <c r="CB16" s="4" t="n">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="CC16" s="4" t="n">
         <v>16</v>
       </c>
       <c r="CD16" s="4" t="n">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="CE16" s="4" t="n">
         <v>0</v>
@@ -4138,13 +4169,13 @@
         <v>0</v>
       </c>
       <c r="CB17" s="4" t="n">
-        <v>774</v>
+        <v>739</v>
       </c>
       <c r="CC17" s="4" t="n">
         <v>27</v>
       </c>
       <c r="CD17" s="4" t="n">
-        <v>801</v>
+        <v>766</v>
       </c>
       <c r="CE17" s="4" t="n">
         <v>0</v>
@@ -4394,13 +4425,13 @@
         <v>0</v>
       </c>
       <c r="CB18" s="4" t="n">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="CC18" s="4" t="n">
         <v>24</v>
       </c>
       <c r="CD18" s="4" t="n">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="CE18" s="4" t="n">
         <v>0</v>
@@ -4906,13 +4937,13 @@
         <v>2</v>
       </c>
       <c r="CB20" s="4" t="n">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="CC20" s="4" t="n">
         <v>12</v>
       </c>
       <c r="CD20" s="4" t="n">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="CE20" s="4" t="n">
         <v>0</v>
@@ -5162,13 +5193,13 @@
         <v>0</v>
       </c>
       <c r="CB21" s="4" t="n">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="CC21" s="4" t="n">
         <v>22</v>
       </c>
       <c r="CD21" s="4" t="n">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="CE21" s="4" t="n">
         <v>0</v>
@@ -5418,13 +5449,13 @@
         <v>0</v>
       </c>
       <c r="CB22" s="4" t="n">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="CC22" s="4" t="n">
         <v>14</v>
       </c>
       <c r="CD22" s="4" t="n">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="CE22" s="4" t="n">
         <v>0</v>
@@ -5674,13 +5705,13 @@
         <v>0</v>
       </c>
       <c r="CB23" s="4" t="n">
-        <v>735</v>
+        <v>713</v>
       </c>
       <c r="CC23" s="4" t="n">
         <v>21</v>
       </c>
       <c r="CD23" s="4" t="n">
-        <v>756</v>
+        <v>734</v>
       </c>
       <c r="CE23" s="4" t="n">
         <v>0</v>
@@ -5930,13 +5961,13 @@
         <v>1</v>
       </c>
       <c r="CB24" s="4" t="n">
-        <v>678</v>
+        <v>656</v>
       </c>
       <c r="CC24" s="4" t="n">
         <v>36</v>
       </c>
       <c r="CD24" s="4" t="n">
-        <v>714</v>
+        <v>692</v>
       </c>
       <c r="CE24" s="4" t="n">
         <v>0</v>
@@ -6186,13 +6217,13 @@
         <v>0</v>
       </c>
       <c r="CB25" s="4" t="n">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="CC25" s="4" t="n">
         <v>16</v>
       </c>
       <c r="CD25" s="4" t="n">
-        <v>614</v>
+        <v>600</v>
       </c>
       <c r="CE25" s="4" t="n">
         <v>0</v>
@@ -6442,13 +6473,13 @@
         <v>3</v>
       </c>
       <c r="CB26" s="4" t="n">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="CC26" s="4" t="n">
         <v>13</v>
       </c>
       <c r="CD26" s="4" t="n">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="CE26" s="4" t="n">
         <v>0</v>
@@ -6698,13 +6729,13 @@
         <v>0</v>
       </c>
       <c r="CB27" s="4" t="n">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="CC27" s="4" t="n">
         <v>28</v>
       </c>
       <c r="CD27" s="4" t="n">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="CE27" s="4" t="n">
         <v>0</v>
@@ -6954,13 +6985,13 @@
         <v>0</v>
       </c>
       <c r="CB28" s="4" t="n">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="CC28" s="4" t="n">
         <v>24</v>
       </c>
       <c r="CD28" s="4" t="n">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="CE28" s="4" t="n">
         <v>0</v>
@@ -7210,13 +7241,13 @@
         <v>0</v>
       </c>
       <c r="CB29" s="4" t="n">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="CC29" s="4" t="n">
         <v>18</v>
       </c>
       <c r="CD29" s="4" t="n">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="CE29" s="4" t="n">
         <v>0</v>
@@ -7722,13 +7753,13 @@
         <v>0</v>
       </c>
       <c r="CB31" s="4" t="n">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="CC31" s="4" t="n">
         <v>32</v>
       </c>
       <c r="CD31" s="4" t="n">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="CE31" s="4" t="n">
         <v>0</v>
@@ -7978,13 +8009,13 @@
         <v>0</v>
       </c>
       <c r="CB32" s="4" t="n">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="CC32" s="4" t="n">
         <v>22</v>
       </c>
       <c r="CD32" s="4" t="n">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="CE32" s="4" t="n">
         <v>0</v>
@@ -8234,13 +8265,13 @@
         <v>0</v>
       </c>
       <c r="CB33" s="4" t="n">
-        <v>635</v>
+        <v>622</v>
       </c>
       <c r="CC33" s="4" t="n">
         <v>26</v>
       </c>
       <c r="CD33" s="4" t="n">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="CE33" s="4" t="n">
         <v>0</v>
@@ -8490,13 +8521,13 @@
         <v>0</v>
       </c>
       <c r="CB34" s="4" t="n">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="CC34" s="4" t="n">
         <v>14</v>
       </c>
       <c r="CD34" s="4" t="n">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="CE34" s="4" t="n">
         <v>0</v>
@@ -8746,13 +8777,13 @@
         <v>1</v>
       </c>
       <c r="CB35" s="4" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="CC35" s="4" t="n">
         <v>35</v>
       </c>
       <c r="CD35" s="4" t="n">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="CE35" s="4" t="n">
         <v>0</v>
@@ -9002,13 +9033,13 @@
         <v>0</v>
       </c>
       <c r="CB36" s="4" t="n">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="CC36" s="4" t="n">
         <v>20</v>
       </c>
       <c r="CD36" s="4" t="n">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="CE36" s="4" t="n">
         <v>0</v>
@@ -9258,13 +9289,13 @@
         <v>0</v>
       </c>
       <c r="CB37" s="4" t="n">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="CC37" s="4" t="n">
         <v>15</v>
       </c>
       <c r="CD37" s="4" t="n">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="CE37" s="4" t="n">
         <v>0</v>
@@ -9514,13 +9545,13 @@
         <v>0</v>
       </c>
       <c r="CB38" s="4" t="n">
-        <v>753</v>
+        <v>727</v>
       </c>
       <c r="CC38" s="4" t="n">
         <v>45</v>
       </c>
       <c r="CD38" s="4" t="n">
-        <v>798</v>
+        <v>772</v>
       </c>
       <c r="CE38" s="4" t="n">
         <v>0</v>
@@ -9770,13 +9801,13 @@
         <v>0</v>
       </c>
       <c r="CB39" s="4" t="n">
-        <v>463</v>
+        <v>443</v>
       </c>
       <c r="CC39" s="4" t="n">
         <v>32</v>
       </c>
       <c r="CD39" s="4" t="n">
-        <v>495</v>
+        <v>475</v>
       </c>
       <c r="CE39" s="4" t="n">
         <v>0</v>
@@ -10026,13 +10057,13 @@
         <v>0</v>
       </c>
       <c r="CB40" s="4" t="n">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="CC40" s="4" t="n">
         <v>2</v>
       </c>
       <c r="CD40" s="4" t="n">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="CE40" s="4" t="n">
         <v>0</v>
@@ -10282,13 +10313,13 @@
         <v>0</v>
       </c>
       <c r="CB41" s="4" t="n">
-        <v>707</v>
+        <v>687</v>
       </c>
       <c r="CC41" s="4" t="n">
         <v>28</v>
       </c>
       <c r="CD41" s="4" t="n">
-        <v>735</v>
+        <v>715</v>
       </c>
       <c r="CE41" s="4" t="n">
         <v>0</v>
@@ -10538,13 +10569,13 @@
         <v>1</v>
       </c>
       <c r="CB42" s="4" t="n">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="CC42" s="4" t="n">
         <v>11</v>
       </c>
       <c r="CD42" s="4" t="n">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="CE42" s="4" t="n">
         <v>0</v>
@@ -11050,13 +11081,13 @@
         <v>0</v>
       </c>
       <c r="CB44" s="4" t="n">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="CC44" s="4" t="n">
         <v>12</v>
       </c>
       <c r="CD44" s="4" t="n">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="CE44" s="4" t="n">
         <v>0</v>
@@ -11306,13 +11337,13 @@
         <v>1</v>
       </c>
       <c r="CB45" s="4" t="n">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="CC45" s="4" t="n">
         <v>22</v>
       </c>
       <c r="CD45" s="4" t="n">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="CE45" s="4" t="n">
         <v>0</v>
@@ -11562,13 +11593,13 @@
         <v>0</v>
       </c>
       <c r="CB46" s="4" t="n">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="CC46" s="4" t="n">
         <v>19</v>
       </c>
       <c r="CD46" s="4" t="n">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="CE46" s="4" t="n">
         <v>0</v>
@@ -11818,13 +11849,13 @@
         <v>0</v>
       </c>
       <c r="CB47" s="4" t="n">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="CC47" s="4" t="n">
         <v>13</v>
       </c>
       <c r="CD47" s="4" t="n">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="CE47" s="4" t="n">
         <v>0</v>
@@ -12074,13 +12105,13 @@
         <v>0</v>
       </c>
       <c r="CB48" s="4" t="n">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="CC48" s="4" t="n">
         <v>13</v>
       </c>
       <c r="CD48" s="4" t="n">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="CE48" s="4" t="n">
         <v>0</v>
@@ -12330,13 +12361,13 @@
         <v>0</v>
       </c>
       <c r="CB49" s="4" t="n">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="CC49" s="4" t="n">
         <v>11</v>
       </c>
       <c r="CD49" s="4" t="n">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="CE49" s="4" t="n">
         <v>0</v>
@@ -12586,13 +12617,13 @@
         <v>1</v>
       </c>
       <c r="CB50" s="4" t="n">
-        <v>725</v>
+        <v>711</v>
       </c>
       <c r="CC50" s="4" t="n">
         <v>15</v>
       </c>
       <c r="CD50" s="4" t="n">
-        <v>740</v>
+        <v>726</v>
       </c>
       <c r="CE50" s="4" t="n">
         <v>0</v>
@@ -12842,13 +12873,13 @@
         <v>1</v>
       </c>
       <c r="CB51" s="4" t="n">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="CC51" s="4" t="n">
         <v>10</v>
       </c>
       <c r="CD51" s="4" t="n">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="CE51" s="4" t="n">
         <v>0</v>
@@ -13354,13 +13385,13 @@
         <v>0</v>
       </c>
       <c r="CB53" s="4" t="n">
-        <v>494</v>
+        <v>473</v>
       </c>
       <c r="CC53" s="4" t="n">
         <v>33</v>
       </c>
       <c r="CD53" s="4" t="n">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="CE53" s="4" t="n">
         <v>0</v>
@@ -13610,13 +13641,13 @@
         <v>2</v>
       </c>
       <c r="CB54" s="4" t="n">
-        <v>673</v>
+        <v>654</v>
       </c>
       <c r="CC54" s="4" t="n">
         <v>35</v>
       </c>
       <c r="CD54" s="4" t="n">
-        <v>708</v>
+        <v>689</v>
       </c>
       <c r="CE54" s="4" t="n">
         <v>0</v>
@@ -13866,13 +13897,13 @@
         <v>1</v>
       </c>
       <c r="CB55" s="4" t="n">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="CC55" s="4" t="n">
         <v>13</v>
       </c>
       <c r="CD55" s="4" t="n">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="CE55" s="4" t="n">
         <v>0</v>
@@ -14122,13 +14153,13 @@
         <v>0</v>
       </c>
       <c r="CB56" s="4" t="n">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="CC56" s="4" t="n">
         <v>12</v>
       </c>
       <c r="CD56" s="4" t="n">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="CE56" s="4" t="n">
         <v>0</v>
@@ -14378,13 +14409,13 @@
         <v>0</v>
       </c>
       <c r="CB57" s="4" t="n">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="CC57" s="4" t="n">
         <v>14</v>
       </c>
       <c r="CD57" s="4" t="n">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="CE57" s="4" t="n">
         <v>0</v>
@@ -14890,13 +14921,13 @@
         <v>1</v>
       </c>
       <c r="CB59" s="4" t="n">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="CC59" s="4" t="n">
         <v>11</v>
       </c>
       <c r="CD59" s="4" t="n">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="CE59" s="4" t="n">
         <v>0</v>
@@ -15402,13 +15433,13 @@
         <v>1</v>
       </c>
       <c r="CB61" s="4" t="n">
-        <v>722</v>
+        <v>707</v>
       </c>
       <c r="CC61" s="4" t="n">
         <v>14</v>
       </c>
       <c r="CD61" s="4" t="n">
-        <v>736</v>
+        <v>721</v>
       </c>
       <c r="CE61" s="4" t="n">
         <v>0</v>
@@ -15658,13 +15689,13 @@
         <v>0</v>
       </c>
       <c r="CB62" s="4" t="n">
-        <v>667</v>
+        <v>651</v>
       </c>
       <c r="CC62" s="4" t="n">
         <v>18</v>
       </c>
       <c r="CD62" s="4" t="n">
-        <v>685</v>
+        <v>669</v>
       </c>
       <c r="CE62" s="4" t="n">
         <v>0</v>
@@ -16170,13 +16201,13 @@
         <v>2</v>
       </c>
       <c r="CB64" s="4" t="n">
-        <v>840</v>
+        <v>821</v>
       </c>
       <c r="CC64" s="4" t="n">
         <v>25</v>
       </c>
       <c r="CD64" s="4" t="n">
-        <v>865</v>
+        <v>846</v>
       </c>
       <c r="CE64" s="4" t="n">
         <v>0</v>
@@ -16426,13 +16457,13 @@
         <v>0</v>
       </c>
       <c r="CB65" s="4" t="n">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="CC65" s="4" t="n">
         <v>11</v>
       </c>
       <c r="CD65" s="4" t="n">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="CE65" s="4" t="n">
         <v>0</v>
@@ -16682,13 +16713,13 @@
         <v>1</v>
       </c>
       <c r="CB66" s="4" t="n">
-        <v>846</v>
+        <v>821</v>
       </c>
       <c r="CC66" s="4" t="n">
         <v>29</v>
       </c>
       <c r="CD66" s="4" t="n">
-        <v>875</v>
+        <v>850</v>
       </c>
       <c r="CE66" s="4" t="n">
         <v>0</v>
@@ -16938,13 +16969,13 @@
         <v>1</v>
       </c>
       <c r="CB67" s="4" t="n">
-        <v>754</v>
+        <v>731</v>
       </c>
       <c r="CC67" s="4" t="n">
         <v>20</v>
       </c>
       <c r="CD67" s="4" t="n">
-        <v>774</v>
+        <v>751</v>
       </c>
       <c r="CE67" s="4" t="n">
         <v>0</v>
@@ -17194,13 +17225,13 @@
         <v>1</v>
       </c>
       <c r="CB68" s="4" t="n">
-        <v>506</v>
+        <v>476</v>
       </c>
       <c r="CC68" s="4" t="n">
         <v>25</v>
       </c>
       <c r="CD68" s="4" t="n">
-        <v>531</v>
+        <v>501</v>
       </c>
       <c r="CE68" s="4" t="n">
         <v>0</v>
@@ -17450,13 +17481,13 @@
         <v>0</v>
       </c>
       <c r="CB69" s="4" t="n">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="CC69" s="4" t="n">
         <v>13</v>
       </c>
       <c r="CD69" s="4" t="n">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="CE69" s="4" t="n">
         <v>0</v>
@@ -17706,13 +17737,13 @@
         <v>2</v>
       </c>
       <c r="CB70" s="4" t="n">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="CC70" s="4" t="n">
         <v>6</v>
       </c>
       <c r="CD70" s="4" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="CE70" s="4" t="n">
         <v>0</v>
@@ -18218,13 +18249,13 @@
         <v>0</v>
       </c>
       <c r="CB72" s="4" t="n">
-        <v>677</v>
+        <v>659</v>
       </c>
       <c r="CC72" s="4" t="n">
         <v>43</v>
       </c>
       <c r="CD72" s="4" t="n">
-        <v>720</v>
+        <v>702</v>
       </c>
       <c r="CE72" s="4" t="n">
         <v>0</v>
@@ -18474,13 +18505,13 @@
         <v>4</v>
       </c>
       <c r="CB73" s="4" t="n">
-        <v>650</v>
+        <v>628</v>
       </c>
       <c r="CC73" s="4" t="n">
         <v>69</v>
       </c>
       <c r="CD73" s="4" t="n">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="CE73" s="4" t="n">
         <v>0</v>
@@ -18730,13 +18761,13 @@
         <v>1</v>
       </c>
       <c r="CB74" s="4" t="n">
-        <v>746</v>
+        <v>718</v>
       </c>
       <c r="CC74" s="4" t="n">
         <v>28</v>
       </c>
       <c r="CD74" s="4" t="n">
-        <v>774</v>
+        <v>746</v>
       </c>
       <c r="CE74" s="4" t="n">
         <v>0</v>
@@ -18986,13 +19017,13 @@
         <v>0</v>
       </c>
       <c r="CB75" s="4" t="n">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="CC75" s="4" t="n">
         <v>11</v>
       </c>
       <c r="CD75" s="4" t="n">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="CE75" s="4" t="n">
         <v>0</v>
@@ -19242,13 +19273,13 @@
         <v>0</v>
       </c>
       <c r="CB76" s="4" t="n">
-        <v>707</v>
+        <v>691</v>
       </c>
       <c r="CC76" s="4" t="n">
         <v>27</v>
       </c>
       <c r="CD76" s="4" t="n">
-        <v>734</v>
+        <v>718</v>
       </c>
       <c r="CE76" s="4" t="n">
         <v>0</v>
@@ -19498,13 +19529,13 @@
         <v>1</v>
       </c>
       <c r="CB77" s="4" t="n">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="CC77" s="4" t="n">
         <v>27</v>
       </c>
       <c r="CD77" s="4" t="n">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="CE77" s="4" t="n">
         <v>0</v>
@@ -19754,13 +19785,13 @@
         <v>0</v>
       </c>
       <c r="CB78" s="4" t="n">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="CC78" s="4" t="n">
         <v>17</v>
       </c>
       <c r="CD78" s="4" t="n">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="CE78" s="4" t="n">
         <v>0</v>
@@ -20010,13 +20041,13 @@
         <v>0</v>
       </c>
       <c r="CB79" s="4" t="n">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="CC79" s="4" t="n">
         <v>14</v>
       </c>
       <c r="CD79" s="4" t="n">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="CE79" s="4" t="n">
         <v>0</v>
@@ -20266,13 +20297,13 @@
         <v>1</v>
       </c>
       <c r="CB80" s="4" t="n">
-        <v>883</v>
+        <v>856</v>
       </c>
       <c r="CC80" s="4" t="n">
         <v>32</v>
       </c>
       <c r="CD80" s="4" t="n">
-        <v>915</v>
+        <v>888</v>
       </c>
       <c r="CE80" s="4" t="n">
         <v>0</v>
@@ -20522,13 +20553,13 @@
         <v>1</v>
       </c>
       <c r="CB81" s="4" t="n">
-        <v>742</v>
+        <v>728</v>
       </c>
       <c r="CC81" s="4" t="n">
         <v>24</v>
       </c>
       <c r="CD81" s="4" t="n">
-        <v>766</v>
+        <v>752</v>
       </c>
       <c r="CE81" s="4" t="n">
         <v>0</v>
@@ -20778,13 +20809,13 @@
         <v>0</v>
       </c>
       <c r="CB82" s="4" t="n">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="CC82" s="4" t="n">
         <v>10</v>
       </c>
       <c r="CD82" s="4" t="n">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="CE82" s="4" t="n">
         <v>0</v>
@@ -21034,13 +21065,13 @@
         <v>0</v>
       </c>
       <c r="CB83" s="4" t="n">
-        <v>771</v>
+        <v>761</v>
       </c>
       <c r="CC83" s="4" t="n">
         <v>14</v>
       </c>
       <c r="CD83" s="4" t="n">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="CE83" s="4" t="n">
         <v>0</v>
@@ -21546,13 +21577,13 @@
         <v>0</v>
       </c>
       <c r="CB85" s="4" t="n">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="CC85" s="4" t="n">
         <v>19</v>
       </c>
       <c r="CD85" s="4" t="n">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="CE85" s="4" t="n">
         <v>0</v>
@@ -22058,13 +22089,13 @@
         <v>0</v>
       </c>
       <c r="CB87" s="4" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="CC87" s="4" t="n">
         <v>6</v>
       </c>
       <c r="CD87" s="4" t="n">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="CE87" s="4" t="n">
         <v>0</v>
@@ -22314,13 +22345,13 @@
         <v>0</v>
       </c>
       <c r="CB88" s="4" t="n">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="CC88" s="4" t="n">
         <v>5</v>
       </c>
       <c r="CD88" s="4" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="CE88" s="4" t="n">
         <v>0</v>
@@ -22570,13 +22601,13 @@
         <v>2</v>
       </c>
       <c r="CB89" s="4" t="n">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="CC89" s="4" t="n">
         <v>2</v>
       </c>
       <c r="CD89" s="4" t="n">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="CE89" s="4" t="n">
         <v>0</v>
@@ -22826,13 +22857,13 @@
         <v>0</v>
       </c>
       <c r="CB90" s="4" t="n">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="CC90" s="4" t="n">
         <v>5</v>
       </c>
       <c r="CD90" s="4" t="n">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="CE90" s="4" t="n">
         <v>0</v>
@@ -23082,13 +23113,13 @@
         <v>1</v>
       </c>
       <c r="CB91" s="4" t="n">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="CC91" s="4" t="n">
         <v>3</v>
       </c>
       <c r="CD91" s="4" t="n">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="CE91" s="4" t="n">
         <v>0</v>
@@ -24362,13 +24393,13 @@
         <v>1</v>
       </c>
       <c r="CB96" s="4" t="n">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="CC96" s="4" t="n">
         <v>13</v>
       </c>
       <c r="CD96" s="4" t="n">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="CE96" s="4" t="n">
         <v>0</v>
@@ -24874,13 +24905,13 @@
         <v>0</v>
       </c>
       <c r="CB98" s="4" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="CC98" s="4" t="n">
         <v>4</v>
       </c>
       <c r="CD98" s="4" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="CE98" s="4" t="n">
         <v>0</v>
@@ -25130,13 +25161,13 @@
         <v>3</v>
       </c>
       <c r="CB99" s="4" t="n">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="CC99" s="4" t="n">
         <v>15</v>
       </c>
       <c r="CD99" s="4" t="n">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="CE99" s="4" t="n">
         <v>0</v>
@@ -25898,13 +25929,13 @@
         <v>0</v>
       </c>
       <c r="CB102" s="4" t="n">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="CC102" s="4" t="n">
         <v>1</v>
       </c>
       <c r="CD102" s="4" t="n">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="CE102" s="4" t="n">
         <v>0</v>
@@ -26154,13 +26185,13 @@
         <v>0</v>
       </c>
       <c r="CB103" s="4" t="n">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="CC103" s="4" t="n">
         <v>11</v>
       </c>
       <c r="CD103" s="4" t="n">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="CE103" s="4" t="n">
         <v>0</v>
@@ -27178,13 +27209,13 @@
         <v>0</v>
       </c>
       <c r="CB107" s="4" t="n">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="CC107" s="4" t="n">
         <v>5</v>
       </c>
       <c r="CD107" s="4" t="n">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="CE107" s="4" t="n">
         <v>0</v>
@@ -27434,13 +27465,13 @@
         <v>1</v>
       </c>
       <c r="CB108" s="4" t="n">
-        <v>839</v>
+        <v>821</v>
       </c>
       <c r="CC108" s="4" t="n">
         <v>31</v>
       </c>
       <c r="CD108" s="4" t="n">
-        <v>870</v>
+        <v>852</v>
       </c>
       <c r="CE108" s="4" t="n">
         <v>0</v>
@@ -27690,13 +27721,13 @@
         <v>0</v>
       </c>
       <c r="CB109" s="4" t="n">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="CC109" s="4" t="n">
         <v>9</v>
       </c>
       <c r="CD109" s="4" t="n">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="CE109" s="4" t="n">
         <v>0</v>
@@ -28458,13 +28489,13 @@
         <v>0</v>
       </c>
       <c r="CB112" s="4" t="n">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="CC112" s="4" t="n">
         <v>14</v>
       </c>
       <c r="CD112" s="4" t="n">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="CE112" s="4" t="n">
         <v>0</v>
@@ -28714,13 +28745,13 @@
         <v>3</v>
       </c>
       <c r="CB113" s="4" t="n">
-        <v>825</v>
+        <v>815</v>
       </c>
       <c r="CC113" s="4" t="n">
         <v>26</v>
       </c>
       <c r="CD113" s="4" t="n">
-        <v>851</v>
+        <v>841</v>
       </c>
       <c r="CE113" s="4" t="n">
         <v>0</v>
@@ -29482,13 +29513,13 @@
         <v>1</v>
       </c>
       <c r="CB116" s="4" t="n">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="CC116" s="4" t="n">
         <v>11</v>
       </c>
       <c r="CD116" s="4" t="n">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="CE116" s="4" t="n">
         <v>0</v>
@@ -29738,13 +29769,13 @@
         <v>1</v>
       </c>
       <c r="CB117" s="4" t="n">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="CC117" s="4" t="n">
         <v>12</v>
       </c>
       <c r="CD117" s="4" t="n">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="CE117" s="4" t="n">
         <v>0</v>
@@ -30762,13 +30793,13 @@
         <v>0</v>
       </c>
       <c r="CB121" s="4" t="n">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="CC121" s="4" t="n">
         <v>23</v>
       </c>
       <c r="CD121" s="4" t="n">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="CE121" s="4" t="n">
         <v>0</v>
@@ -31274,13 +31305,13 @@
         <v>0</v>
       </c>
       <c r="CB123" s="4" t="n">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="CC123" s="4" t="n">
         <v>14</v>
       </c>
       <c r="CD123" s="4" t="n">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="CE123" s="4" t="n">
         <v>0</v>
@@ -31530,13 +31561,13 @@
         <v>0</v>
       </c>
       <c r="CB124" s="4" t="n">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="CC124" s="4" t="n">
         <v>13</v>
       </c>
       <c r="CD124" s="4" t="n">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="CE124" s="4" t="n">
         <v>0</v>
@@ -31786,13 +31817,13 @@
         <v>2</v>
       </c>
       <c r="CB125" s="4" t="n">
-        <v>730</v>
+        <v>716</v>
       </c>
       <c r="CC125" s="4" t="n">
         <v>15</v>
       </c>
       <c r="CD125" s="4" t="n">
-        <v>745</v>
+        <v>731</v>
       </c>
       <c r="CE125" s="4" t="n">
         <v>0</v>
@@ -32042,13 +32073,13 @@
         <v>0</v>
       </c>
       <c r="CB126" s="4" t="n">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="CC126" s="4" t="n">
         <v>1</v>
       </c>
       <c r="CD126" s="4" t="n">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="CE126" s="4" t="n">
         <v>0</v>
@@ -32298,13 +32329,13 @@
         <v>0</v>
       </c>
       <c r="CB127" s="4" t="n">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="CC127" s="4" t="n">
         <v>4</v>
       </c>
       <c r="CD127" s="4" t="n">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="CE127" s="4" t="n">
         <v>0</v>
@@ -32554,13 +32585,13 @@
         <v>1</v>
       </c>
       <c r="CB128" s="4" t="n">
-        <v>732</v>
+        <v>723</v>
       </c>
       <c r="CC128" s="4" t="n">
         <v>6</v>
       </c>
       <c r="CD128" s="4" t="n">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="CE128" s="4" t="n">
         <v>0</v>
@@ -32810,13 +32841,13 @@
         <v>0</v>
       </c>
       <c r="CB129" s="4" t="n">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="CC129" s="4" t="n">
         <v>8</v>
       </c>
       <c r="CD129" s="4" t="n">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="CE129" s="4" t="n">
         <v>0</v>
@@ -33066,13 +33097,13 @@
         <v>0</v>
       </c>
       <c r="CB130" s="4" t="n">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="CC130" s="4" t="n">
         <v>15</v>
       </c>
       <c r="CD130" s="4" t="n">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="CE130" s="4" t="n">
         <v>0</v>
@@ -33578,13 +33609,13 @@
         <v>0</v>
       </c>
       <c r="CB132" s="4" t="n">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="CC132" s="4" t="n">
         <v>6</v>
       </c>
       <c r="CD132" s="4" t="n">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="CE132" s="4" t="n">
         <v>0</v>
@@ -33834,13 +33865,13 @@
         <v>2</v>
       </c>
       <c r="CB133" s="4" t="n">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="CC133" s="4" t="n">
         <v>22</v>
       </c>
       <c r="CD133" s="4" t="n">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="CE133" s="4" t="n">
         <v>0</v>
@@ -34090,13 +34121,13 @@
         <v>3</v>
       </c>
       <c r="CB134" s="4" t="n">
-        <v>983</v>
+        <v>973</v>
       </c>
       <c r="CC134" s="4" t="n">
         <v>19</v>
       </c>
       <c r="CD134" s="4" t="n">
-        <v>1002</v>
+        <v>992</v>
       </c>
       <c r="CE134" s="4" t="n">
         <v>0</v>
@@ -34346,13 +34377,13 @@
         <v>2</v>
       </c>
       <c r="CB135" s="4" t="n">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="CC135" s="4" t="n">
         <v>8</v>
       </c>
       <c r="CD135" s="4" t="n">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="CE135" s="4" t="n">
         <v>0</v>
@@ -34602,13 +34633,13 @@
         <v>0</v>
       </c>
       <c r="CB136" s="4" t="n">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="CC136" s="4" t="n">
         <v>26</v>
       </c>
       <c r="CD136" s="4" t="n">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="CE136" s="4" t="n">
         <v>0</v>
@@ -34858,13 +34889,13 @@
         <v>0</v>
       </c>
       <c r="CB137" s="4" t="n">
-        <v>907</v>
+        <v>875</v>
       </c>
       <c r="CC137" s="4" t="n">
         <v>52</v>
       </c>
       <c r="CD137" s="4" t="n">
-        <v>959</v>
+        <v>927</v>
       </c>
       <c r="CE137" s="4" t="n">
         <v>0</v>
@@ -35114,13 +35145,13 @@
         <v>1</v>
       </c>
       <c r="CB138" s="4" t="n">
-        <v>685</v>
+        <v>667</v>
       </c>
       <c r="CC138" s="4" t="n">
         <v>25</v>
       </c>
       <c r="CD138" s="4" t="n">
-        <v>710</v>
+        <v>692</v>
       </c>
       <c r="CE138" s="4" t="n">
         <v>0</v>
@@ -35626,13 +35657,13 @@
         <v>0</v>
       </c>
       <c r="CB140" s="4" t="n">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="CC140" s="4" t="n">
         <v>0</v>
       </c>
       <c r="CD140" s="4" t="n">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="CE140" s="4" t="n">
         <v>0</v>
@@ -35882,13 +35913,13 @@
         <v>0</v>
       </c>
       <c r="CB141" s="4" t="n">
-        <v>724</v>
+        <v>682</v>
       </c>
       <c r="CC141" s="4" t="n">
         <v>34</v>
       </c>
       <c r="CD141" s="4" t="n">
-        <v>758</v>
+        <v>716</v>
       </c>
       <c r="CE141" s="4" t="n">
         <v>0</v>
@@ -36138,13 +36169,13 @@
         <v>0</v>
       </c>
       <c r="CB142" s="4" t="n">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="CC142" s="4" t="n">
         <v>12</v>
       </c>
       <c r="CD142" s="4" t="n">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="CE142" s="4" t="n">
         <v>0</v>
@@ -36394,13 +36425,13 @@
         <v>0</v>
       </c>
       <c r="CB143" s="4" t="n">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="CC143" s="4" t="n">
         <v>13</v>
       </c>
       <c r="CD143" s="4" t="n">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="CE143" s="4" t="n">
         <v>0</v>
@@ -36650,13 +36681,13 @@
         <v>0</v>
       </c>
       <c r="CB144" s="4" t="n">
-        <v>761</v>
+        <v>739</v>
       </c>
       <c r="CC144" s="4" t="n">
         <v>41</v>
       </c>
       <c r="CD144" s="4" t="n">
-        <v>802</v>
+        <v>780</v>
       </c>
       <c r="CE144" s="4" t="n">
         <v>0</v>
@@ -36906,13 +36937,13 @@
         <v>1</v>
       </c>
       <c r="CB145" s="4" t="n">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="CC145" s="4" t="n">
         <v>15</v>
       </c>
       <c r="CD145" s="4" t="n">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="CE145" s="4" t="n">
         <v>0</v>
@@ -37162,13 +37193,13 @@
         <v>1</v>
       </c>
       <c r="CB146" s="4" t="n">
-        <v>749</v>
+        <v>716</v>
       </c>
       <c r="CC146" s="4" t="n">
         <v>48</v>
       </c>
       <c r="CD146" s="4" t="n">
-        <v>797</v>
+        <v>764</v>
       </c>
       <c r="CE146" s="4" t="n">
         <v>0</v>
@@ -37418,13 +37449,13 @@
         <v>2</v>
       </c>
       <c r="CB147" s="4" t="n">
-        <v>849</v>
+        <v>839</v>
       </c>
       <c r="CC147" s="4" t="n">
         <v>20</v>
       </c>
       <c r="CD147" s="4" t="n">
-        <v>869</v>
+        <v>859</v>
       </c>
       <c r="CE147" s="4" t="n">
         <v>0</v>
@@ -37674,13 +37705,13 @@
         <v>0</v>
       </c>
       <c r="CB148" s="4" t="n">
-        <v>819</v>
+        <v>804</v>
       </c>
       <c r="CC148" s="4" t="n">
         <v>34</v>
       </c>
       <c r="CD148" s="4" t="n">
-        <v>853</v>
+        <v>838</v>
       </c>
       <c r="CE148" s="4" t="n">
         <v>0</v>
@@ -37930,13 +37961,13 @@
         <v>2</v>
       </c>
       <c r="CB149" s="4" t="n">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="CC149" s="4" t="n">
         <v>19</v>
       </c>
       <c r="CD149" s="4" t="n">
-        <v>852</v>
+        <v>845</v>
       </c>
       <c r="CE149" s="4" t="n">
         <v>0</v>
@@ -38186,13 +38217,13 @@
         <v>0</v>
       </c>
       <c r="CB150" s="4" t="n">
-        <v>840</v>
+        <v>817</v>
       </c>
       <c r="CC150" s="4" t="n">
         <v>21</v>
       </c>
       <c r="CD150" s="4" t="n">
-        <v>861</v>
+        <v>838</v>
       </c>
       <c r="CE150" s="4" t="n">
         <v>0</v>
@@ -38442,13 +38473,13 @@
         <v>1</v>
       </c>
       <c r="CB151" s="4" t="n">
-        <v>610</v>
+        <v>594</v>
       </c>
       <c r="CC151" s="4" t="n">
         <v>8</v>
       </c>
       <c r="CD151" s="4" t="n">
-        <v>618</v>
+        <v>602</v>
       </c>
       <c r="CE151" s="4" t="n">
         <v>0</v>
@@ -38698,13 +38729,13 @@
         <v>0</v>
       </c>
       <c r="CB152" s="4" t="n">
-        <v>772</v>
+        <v>760</v>
       </c>
       <c r="CC152" s="4" t="n">
         <v>15</v>
       </c>
       <c r="CD152" s="4" t="n">
-        <v>787</v>
+        <v>775</v>
       </c>
       <c r="CE152" s="4" t="n">
         <v>0</v>
@@ -38954,13 +38985,13 @@
         <v>0</v>
       </c>
       <c r="CB153" s="4" t="n">
-        <v>541</v>
+        <v>519</v>
       </c>
       <c r="CC153" s="4" t="n">
         <v>16</v>
       </c>
       <c r="CD153" s="4" t="n">
-        <v>557</v>
+        <v>535</v>
       </c>
       <c r="CE153" s="4" t="n">
         <v>0</v>
@@ -39210,13 +39241,13 @@
         <v>0</v>
       </c>
       <c r="CB154" s="4" t="n">
-        <v>643</v>
+        <v>626</v>
       </c>
       <c r="CC154" s="4" t="n">
         <v>28</v>
       </c>
       <c r="CD154" s="4" t="n">
-        <v>671</v>
+        <v>654</v>
       </c>
       <c r="CE154" s="4" t="n">
         <v>0</v>
@@ -39466,13 +39497,13 @@
         <v>14</v>
       </c>
       <c r="CB155" s="4" t="n">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="CC155" s="4" t="n">
         <v>0</v>
       </c>
       <c r="CD155" s="4" t="n">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="CE155" s="4" t="n">
         <v>0</v>
@@ -39722,13 +39753,13 @@
         <v>0</v>
       </c>
       <c r="CB156" s="4" t="n">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="CC156" s="4" t="n">
         <v>18</v>
       </c>
       <c r="CD156" s="4" t="n">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="CE156" s="4" t="n">
         <v>0</v>
@@ -39978,13 +40009,13 @@
         <v>0</v>
       </c>
       <c r="CB157" s="4" t="n">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="CC157" s="4" t="n">
         <v>7</v>
       </c>
       <c r="CD157" s="4" t="n">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="CE157" s="4" t="n">
         <v>0</v>
@@ -40234,13 +40265,13 @@
         <v>0</v>
       </c>
       <c r="CB158" s="4" t="n">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="CC158" s="4" t="n">
         <v>25</v>
       </c>
       <c r="CD158" s="4" t="n">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="CE158" s="4" t="n">
         <v>0</v>
@@ -40490,13 +40521,13 @@
         <v>0</v>
       </c>
       <c r="CB159" s="4" t="n">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="CC159" s="4" t="n">
         <v>17</v>
       </c>
       <c r="CD159" s="4" t="n">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="CE159" s="4" t="n">
         <v>0</v>
@@ -40746,13 +40777,13 @@
         <v>0</v>
       </c>
       <c r="CB160" s="4" t="n">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="CC160" s="4" t="n">
         <v>29</v>
       </c>
       <c r="CD160" s="4" t="n">
-        <v>700</v>
+        <v>688</v>
       </c>
       <c r="CE160" s="4" t="n">
         <v>0</v>
@@ -41002,13 +41033,13 @@
         <v>0</v>
       </c>
       <c r="CB161" s="4" t="n">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="CC161" s="4" t="n">
         <v>20</v>
       </c>
       <c r="CD161" s="4" t="n">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="CE161" s="4" t="n">
         <v>0</v>
@@ -41258,13 +41289,13 @@
         <v>0</v>
       </c>
       <c r="CB162" s="4" t="n">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="CC162" s="4" t="n">
         <v>21</v>
       </c>
       <c r="CD162" s="4" t="n">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="CE162" s="4" t="n">
         <v>0</v>
@@ -41514,13 +41545,13 @@
         <v>0</v>
       </c>
       <c r="CB163" s="4" t="n">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="CC163" s="4" t="n">
         <v>10</v>
       </c>
       <c r="CD163" s="4" t="n">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="CE163" s="4" t="n">
         <v>0</v>
@@ -41770,13 +41801,13 @@
         <v>0</v>
       </c>
       <c r="CB164" s="4" t="n">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="CC164" s="4" t="n">
         <v>11</v>
       </c>
       <c r="CD164" s="4" t="n">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="CE164" s="4" t="n">
         <v>0</v>
@@ -42026,13 +42057,13 @@
         <v>2</v>
       </c>
       <c r="CB165" s="4" t="n">
-        <v>828</v>
+        <v>807</v>
       </c>
       <c r="CC165" s="4" t="n">
         <v>41</v>
       </c>
       <c r="CD165" s="4" t="n">
-        <v>869</v>
+        <v>848</v>
       </c>
       <c r="CE165" s="4" t="n">
         <v>0</v>
@@ -42282,13 +42313,13 @@
         <v>0</v>
       </c>
       <c r="CB166" s="4" t="n">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="CC166" s="4" t="n">
         <v>4</v>
       </c>
       <c r="CD166" s="4" t="n">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="CE166" s="4" t="n">
         <v>0</v>
@@ -42538,13 +42569,13 @@
         <v>2</v>
       </c>
       <c r="CB167" s="4" t="n">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="CC167" s="4" t="n">
         <v>6</v>
       </c>
       <c r="CD167" s="4" t="n">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="CE167" s="4" t="n">
         <v>0</v>
@@ -42794,13 +42825,13 @@
         <v>0</v>
       </c>
       <c r="CB168" s="4" t="n">
-        <v>637</v>
+        <v>614</v>
       </c>
       <c r="CC168" s="4" t="n">
         <v>15</v>
       </c>
       <c r="CD168" s="4" t="n">
-        <v>652</v>
+        <v>629</v>
       </c>
       <c r="CE168" s="4" t="n">
         <v>0</v>
@@ -43050,13 +43081,13 @@
         <v>0</v>
       </c>
       <c r="CB169" s="4" t="n">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="CC169" s="4" t="n">
         <v>7</v>
       </c>
       <c r="CD169" s="4" t="n">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="CE169" s="4" t="n">
         <v>0</v>
@@ -43306,13 +43337,13 @@
         <v>0</v>
       </c>
       <c r="CB170" s="4" t="n">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="CC170" s="4" t="n">
         <v>10</v>
       </c>
       <c r="CD170" s="4" t="n">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="CE170" s="4" t="n">
         <v>0</v>
@@ -43562,13 +43593,13 @@
         <v>2</v>
       </c>
       <c r="CB171" s="4" t="n">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="CC171" s="4" t="n">
         <v>35</v>
       </c>
       <c r="CD171" s="4" t="n">
-        <v>687</v>
+        <v>674</v>
       </c>
       <c r="CE171" s="4" t="n">
         <v>0</v>
@@ -43818,13 +43849,13 @@
         <v>0</v>
       </c>
       <c r="CB172" s="4" t="n">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="CC172" s="4" t="n">
         <v>18</v>
       </c>
       <c r="CD172" s="4" t="n">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="CE172" s="4" t="n">
         <v>0</v>
@@ -44074,13 +44105,13 @@
         <v>0</v>
       </c>
       <c r="CB173" s="4" t="n">
-        <v>718</v>
+        <v>703</v>
       </c>
       <c r="CC173" s="4" t="n">
         <v>37</v>
       </c>
       <c r="CD173" s="4" t="n">
-        <v>755</v>
+        <v>740</v>
       </c>
       <c r="CE173" s="4" t="n">
         <v>0</v>
@@ -44330,13 +44361,13 @@
         <v>0</v>
       </c>
       <c r="CB174" s="4" t="n">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="CC174" s="4" t="n">
         <v>12</v>
       </c>
       <c r="CD174" s="4" t="n">
-        <v>636</v>
+        <v>622</v>
       </c>
       <c r="CE174" s="4" t="n">
         <v>0</v>
@@ -44586,13 +44617,13 @@
         <v>0</v>
       </c>
       <c r="CB175" s="4" t="n">
-        <v>648</v>
+        <v>633</v>
       </c>
       <c r="CC175" s="4" t="n">
         <v>19</v>
       </c>
       <c r="CD175" s="4" t="n">
-        <v>667</v>
+        <v>652</v>
       </c>
       <c r="CE175" s="4" t="n">
         <v>0</v>
@@ -44842,13 +44873,13 @@
         <v>0</v>
       </c>
       <c r="CB176" s="4" t="n">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="CC176" s="4" t="n">
         <v>22</v>
       </c>
       <c r="CD176" s="4" t="n">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="CE176" s="4" t="n">
         <v>0</v>
@@ -45098,13 +45129,13 @@
         <v>0</v>
       </c>
       <c r="CB177" s="4" t="n">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="CC177" s="4" t="n">
         <v>19</v>
       </c>
       <c r="CD177" s="4" t="n">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="CE177" s="4" t="n">
         <v>0</v>
@@ -45354,13 +45385,13 @@
         <v>0</v>
       </c>
       <c r="CB178" s="4" t="n">
-        <v>539</v>
+        <v>525</v>
       </c>
       <c r="CC178" s="4" t="n">
         <v>29</v>
       </c>
       <c r="CD178" s="4" t="n">
-        <v>568</v>
+        <v>554</v>
       </c>
       <c r="CE178" s="4" t="n">
         <v>0</v>
@@ -45610,13 +45641,13 @@
         <v>0</v>
       </c>
       <c r="CB179" s="4" t="n">
-        <v>685</v>
+        <v>668</v>
       </c>
       <c r="CC179" s="4" t="n">
         <v>43</v>
       </c>
       <c r="CD179" s="4" t="n">
-        <v>728</v>
+        <v>711</v>
       </c>
       <c r="CE179" s="4" t="n">
         <v>0</v>
@@ -45866,13 +45897,13 @@
         <v>1</v>
       </c>
       <c r="CB180" s="4" t="n">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="CC180" s="4" t="n">
         <v>19</v>
       </c>
       <c r="CD180" s="4" t="n">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="CE180" s="4" t="n">
         <v>0</v>
@@ -46122,13 +46153,13 @@
         <v>0</v>
       </c>
       <c r="CB181" s="4" t="n">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="CC181" s="4" t="n">
         <v>37</v>
       </c>
       <c r="CD181" s="4" t="n">
-        <v>721</v>
+        <v>708</v>
       </c>
       <c r="CE181" s="4" t="n">
         <v>0</v>
@@ -46378,13 +46409,13 @@
         <v>0</v>
       </c>
       <c r="CB182" s="4" t="n">
-        <v>662</v>
+        <v>639</v>
       </c>
       <c r="CC182" s="4" t="n">
         <v>53</v>
       </c>
       <c r="CD182" s="4" t="n">
-        <v>715</v>
+        <v>692</v>
       </c>
       <c r="CE182" s="4" t="n">
         <v>0</v>
@@ -46634,13 +46665,13 @@
         <v>0</v>
       </c>
       <c r="CB183" s="4" t="n">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="CC183" s="4" t="n">
         <v>26</v>
       </c>
       <c r="CD183" s="4" t="n">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="CE183" s="4" t="n">
         <v>0</v>
@@ -46890,13 +46921,13 @@
         <v>0</v>
       </c>
       <c r="CB184" s="4" t="n">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="CC184" s="4" t="n">
         <v>17</v>
       </c>
       <c r="CD184" s="4" t="n">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="CE184" s="4" t="n">
         <v>0</v>
@@ -47146,13 +47177,13 @@
         <v>2</v>
       </c>
       <c r="CB185" s="4" t="n">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="CC185" s="4" t="n">
         <v>11</v>
       </c>
       <c r="CD185" s="4" t="n">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="CE185" s="4" t="n">
         <v>0</v>
@@ -47402,13 +47433,13 @@
         <v>0</v>
       </c>
       <c r="CB186" s="4" t="n">
-        <v>793</v>
+        <v>773</v>
       </c>
       <c r="CC186" s="4" t="n">
         <v>25</v>
       </c>
       <c r="CD186" s="4" t="n">
-        <v>818</v>
+        <v>798</v>
       </c>
       <c r="CE186" s="4" t="n">
         <v>0</v>
@@ -47658,13 +47689,13 @@
         <v>0</v>
       </c>
       <c r="CB187" s="4" t="n">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="CC187" s="4" t="n">
         <v>6</v>
       </c>
       <c r="CD187" s="4" t="n">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="CE187" s="4" t="n">
         <v>0</v>
@@ -47914,13 +47945,13 @@
         <v>0</v>
       </c>
       <c r="CB188" s="4" t="n">
-        <v>609</v>
+        <v>591</v>
       </c>
       <c r="CC188" s="4" t="n">
         <v>24</v>
       </c>
       <c r="CD188" s="4" t="n">
-        <v>633</v>
+        <v>615</v>
       </c>
       <c r="CE188" s="4" t="n">
         <v>0</v>
@@ -48170,13 +48201,13 @@
         <v>0</v>
       </c>
       <c r="CB189" s="4" t="n">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="CC189" s="4" t="n">
         <v>35</v>
       </c>
       <c r="CD189" s="4" t="n">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="CE189" s="4" t="n">
         <v>0</v>
@@ -48939,13 +48970,13 @@
         <v>2</v>
       </c>
       <c r="CB192" s="4" t="n">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="CC192" s="4" t="n">
         <v>11</v>
       </c>
       <c r="CD192" s="4" t="n">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="CE192" s="4" t="n">
         <v>0</v>
@@ -49195,13 +49226,13 @@
         <v>1</v>
       </c>
       <c r="CB193" s="4" t="n">
-        <v>758</v>
+        <v>741</v>
       </c>
       <c r="CC193" s="4" t="n">
         <v>13</v>
       </c>
       <c r="CD193" s="4" t="n">
-        <v>771</v>
+        <v>754</v>
       </c>
       <c r="CE193" s="4" t="n">
         <v>0</v>
@@ -49451,13 +49482,13 @@
         <v>0</v>
       </c>
       <c r="CB194" s="4" t="n">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="CC194" s="4" t="n">
         <v>18</v>
       </c>
       <c r="CD194" s="4" t="n">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="CE194" s="4" t="n">
         <v>0</v>
@@ -49707,13 +49738,13 @@
         <v>0</v>
       </c>
       <c r="CB195" s="4" t="n">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="CC195" s="4" t="n">
         <v>12</v>
       </c>
       <c r="CD195" s="4" t="n">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="CE195" s="4" t="n">
         <v>0</v>
@@ -49963,13 +49994,13 @@
         <v>0</v>
       </c>
       <c r="CB196" s="4" t="n">
-        <v>771</v>
+        <v>751</v>
       </c>
       <c r="CC196" s="4" t="n">
         <v>0</v>
       </c>
       <c r="CD196" s="4" t="n">
-        <v>771</v>
+        <v>751</v>
       </c>
       <c r="CE196" s="4" t="n">
         <v>0</v>
@@ -50219,13 +50250,13 @@
         <v>2</v>
       </c>
       <c r="CB197" s="4" t="n">
-        <v>678</v>
+        <v>664</v>
       </c>
       <c r="CC197" s="4" t="n">
         <v>23</v>
       </c>
       <c r="CD197" s="4" t="n">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="CE197" s="4" t="n">
         <v>0</v>
@@ -50475,13 +50506,13 @@
         <v>0</v>
       </c>
       <c r="CB198" s="4" t="n">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="CC198" s="4" t="n">
         <v>35</v>
       </c>
       <c r="CD198" s="4" t="n">
-        <v>628</v>
+        <v>609</v>
       </c>
       <c r="CE198" s="4" t="n">
         <v>0</v>
@@ -50731,13 +50762,13 @@
         <v>0</v>
       </c>
       <c r="CB199" s="4" t="n">
-        <v>727</v>
+        <v>709</v>
       </c>
       <c r="CC199" s="4" t="n">
         <v>49</v>
       </c>
       <c r="CD199" s="4" t="n">
-        <v>776</v>
+        <v>758</v>
       </c>
       <c r="CE199" s="4" t="n">
         <v>0</v>
@@ -50987,13 +51018,13 @@
         <v>0</v>
       </c>
       <c r="CB200" s="4" t="n">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="CC200" s="4" t="n">
         <v>36</v>
       </c>
       <c r="CD200" s="4" t="n">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="CE200" s="4" t="n">
         <v>0</v>
@@ -51243,13 +51274,13 @@
         <v>0</v>
       </c>
       <c r="CB201" s="4" t="n">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="CC201" s="4" t="n">
         <v>10</v>
       </c>
       <c r="CD201" s="4" t="n">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="CE201" s="4" t="n">
         <v>0</v>
@@ -51499,13 +51530,13 @@
         <v>0</v>
       </c>
       <c r="CB202" s="4" t="n">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="CC202" s="4" t="n">
         <v>20</v>
       </c>
       <c r="CD202" s="4" t="n">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="CE202" s="4" t="n">
         <v>0</v>
@@ -51755,13 +51786,13 @@
         <v>0</v>
       </c>
       <c r="CB203" s="4" t="n">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="CC203" s="4" t="n">
         <v>15</v>
       </c>
       <c r="CD203" s="4" t="n">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="CE203" s="4" t="n">
         <v>0</v>
@@ -52011,13 +52042,13 @@
         <v>0</v>
       </c>
       <c r="CB204" s="4" t="n">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="CC204" s="4" t="n">
         <v>20</v>
       </c>
       <c r="CD204" s="4" t="n">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="CE204" s="4" t="n">
         <v>0</v>
@@ -52267,13 +52298,13 @@
         <v>1</v>
       </c>
       <c r="CB205" s="4" t="n">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="CC205" s="4" t="n">
         <v>26</v>
       </c>
       <c r="CD205" s="4" t="n">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="CE205" s="4" t="n">
         <v>0</v>
@@ -52523,13 +52554,13 @@
         <v>1</v>
       </c>
       <c r="CB206" s="4" t="n">
-        <v>664</v>
+        <v>641</v>
       </c>
       <c r="CC206" s="4" t="n">
         <v>38</v>
       </c>
       <c r="CD206" s="4" t="n">
-        <v>702</v>
+        <v>679</v>
       </c>
       <c r="CE206" s="4" t="n">
         <v>0</v>
@@ -52779,13 +52810,13 @@
         <v>0</v>
       </c>
       <c r="CB207" s="4" t="n">
-        <v>808</v>
+        <v>788</v>
       </c>
       <c r="CC207" s="4" t="n">
         <v>10</v>
       </c>
       <c r="CD207" s="4" t="n">
-        <v>818</v>
+        <v>798</v>
       </c>
       <c r="CE207" s="4" t="n">
         <v>0</v>
@@ -53035,13 +53066,13 @@
         <v>2</v>
       </c>
       <c r="CB208" s="4" t="n">
-        <v>899</v>
+        <v>880</v>
       </c>
       <c r="CC208" s="4" t="n">
         <v>16</v>
       </c>
       <c r="CD208" s="4" t="n">
-        <v>915</v>
+        <v>896</v>
       </c>
       <c r="CE208" s="4" t="n">
         <v>0</v>
@@ -53291,13 +53322,13 @@
         <v>0</v>
       </c>
       <c r="CB209" s="4" t="n">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="CC209" s="4" t="n">
         <v>6</v>
       </c>
       <c r="CD209" s="4" t="n">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="CE209" s="4" t="n">
         <v>0</v>
@@ -53548,13 +53579,13 @@
         <v>0</v>
       </c>
       <c r="CB210" s="4" t="n">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="CC210" s="4" t="n">
         <v>16</v>
       </c>
       <c r="CD210" s="4" t="n">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="CE210" s="4" t="n">
         <v>0</v>
@@ -53804,13 +53835,13 @@
         <v>0</v>
       </c>
       <c r="CB211" s="4" t="n">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="CC211" s="4" t="n">
         <v>6</v>
       </c>
       <c r="CD211" s="4" t="n">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="CE211" s="4" t="n">
         <v>0</v>
@@ -54060,13 +54091,13 @@
         <v>1</v>
       </c>
       <c r="CB212" s="4" t="n">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="CC212" s="4" t="n">
         <v>18</v>
       </c>
       <c r="CD212" s="4" t="n">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="CE212" s="4" t="n">
         <v>0</v>
@@ -54317,13 +54348,13 @@
         <v>1</v>
       </c>
       <c r="CB213" s="4" t="n">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="CC213" s="4" t="n">
         <v>36</v>
       </c>
       <c r="CD213" s="4" t="n">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="CE213" s="4" t="n">
         <v>0</v>
@@ -54573,13 +54604,13 @@
         <v>0</v>
       </c>
       <c r="CB214" s="4" t="n">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="CC214" s="4" t="n">
         <v>28</v>
       </c>
       <c r="CD214" s="4" t="n">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="CE214" s="4" t="n">
         <v>0</v>
@@ -54829,13 +54860,13 @@
         <v>1</v>
       </c>
       <c r="CB215" s="4" t="n">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="CC215" s="4" t="n">
         <v>20</v>
       </c>
       <c r="CD215" s="4" t="n">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="CE215" s="4" t="n">
         <v>0</v>
@@ -55085,13 +55116,13 @@
         <v>0</v>
       </c>
       <c r="CB216" s="4" t="n">
-        <v>744</v>
+        <v>724</v>
       </c>
       <c r="CC216" s="4" t="n">
         <v>65</v>
       </c>
       <c r="CD216" s="4" t="n">
-        <v>809</v>
+        <v>789</v>
       </c>
       <c r="CE216" s="4" t="n">
         <v>0</v>
@@ -55341,13 +55372,13 @@
         <v>1</v>
       </c>
       <c r="CB217" s="4" t="n">
-        <v>757</v>
+        <v>733</v>
       </c>
       <c r="CC217" s="4" t="n">
         <v>41</v>
       </c>
       <c r="CD217" s="4" t="n">
-        <v>798</v>
+        <v>774</v>
       </c>
       <c r="CE217" s="4" t="n">
         <v>0</v>
@@ -55597,13 +55628,13 @@
         <v>0</v>
       </c>
       <c r="CB218" s="4" t="n">
-        <v>677</v>
+        <v>662</v>
       </c>
       <c r="CC218" s="4" t="n">
         <v>7</v>
       </c>
       <c r="CD218" s="4" t="n">
-        <v>684</v>
+        <v>669</v>
       </c>
       <c r="CE218" s="4" t="n">
         <v>0</v>
@@ -55853,13 +55884,13 @@
         <v>0</v>
       </c>
       <c r="CB219" s="4" t="n">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="CC219" s="4" t="n">
         <v>15</v>
       </c>
       <c r="CD219" s="4" t="n">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="CE219" s="4" t="n">
         <v>0</v>
@@ -56109,13 +56140,13 @@
         <v>0</v>
       </c>
       <c r="CB220" s="4" t="n">
-        <v>689</v>
+        <v>673</v>
       </c>
       <c r="CC220" s="4" t="n">
         <v>22</v>
       </c>
       <c r="CD220" s="4" t="n">
-        <v>711</v>
+        <v>695</v>
       </c>
       <c r="CE220" s="4" t="n">
         <v>0</v>
@@ -56365,13 +56396,13 @@
         <v>0</v>
       </c>
       <c r="CB221" s="4" t="n">
-        <v>574</v>
+        <v>554</v>
       </c>
       <c r="CC221" s="4" t="n">
         <v>39</v>
       </c>
       <c r="CD221" s="4" t="n">
-        <v>613</v>
+        <v>593</v>
       </c>
       <c r="CE221" s="4" t="n">
         <v>0</v>
@@ -56621,13 +56652,13 @@
         <v>0</v>
       </c>
       <c r="CB222" s="4" t="n">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="CC222" s="4" t="n">
         <v>30</v>
       </c>
       <c r="CD222" s="4" t="n">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="CE222" s="4" t="n">
         <v>0</v>
@@ -56877,13 +56908,13 @@
         <v>0</v>
       </c>
       <c r="CB223" s="4" t="n">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="CC223" s="4" t="n">
         <v>13</v>
       </c>
       <c r="CD223" s="4" t="n">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="CE223" s="4" t="n">
         <v>0</v>
@@ -57133,13 +57164,13 @@
         <v>0</v>
       </c>
       <c r="CB224" s="4" t="n">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="CC224" s="4" t="n">
         <v>7</v>
       </c>
       <c r="CD224" s="4" t="n">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="CE224" s="4" t="n">
         <v>0</v>
@@ -57389,13 +57420,13 @@
         <v>0</v>
       </c>
       <c r="CB225" s="4" t="n">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="CC225" s="4" t="n">
         <v>10</v>
       </c>
       <c r="CD225" s="4" t="n">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="CE225" s="4" t="n">
         <v>0</v>
@@ -57645,13 +57676,13 @@
         <v>0</v>
       </c>
       <c r="CB226" s="4" t="n">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="CC226" s="4" t="n">
         <v>36</v>
       </c>
       <c r="CD226" s="4" t="n">
-        <v>792</v>
+        <v>774</v>
       </c>
       <c r="CE226" s="4" t="n">
         <v>0</v>
@@ -57901,13 +57932,13 @@
         <v>0</v>
       </c>
       <c r="CB227" s="4" t="n">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="CC227" s="4" t="n">
         <v>12</v>
       </c>
       <c r="CD227" s="4" t="n">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="CE227" s="4" t="n">
         <v>0</v>
@@ -58157,13 +58188,13 @@
         <v>0</v>
       </c>
       <c r="CB228" s="4" t="n">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="CC228" s="4" t="n">
         <v>16</v>
       </c>
       <c r="CD228" s="4" t="n">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="CE228" s="4" t="n">
         <v>0</v>
@@ -58173,927 +58204,927 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="8" t="inlineStr">
+      <c r="A229" s="15" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B229" s="13" t="inlineStr"/>
-      <c r="C229" s="14">
+      <c r="B229" s="16" t="inlineStr"/>
+      <c r="C229" s="17">
         <f>SUM(C6:C228)</f>
         <v/>
       </c>
-      <c r="D229" s="14">
+      <c r="D229" s="17">
         <f>SUM(D6:D228)</f>
         <v/>
       </c>
-      <c r="E229" s="14">
+      <c r="E229" s="17">
         <f>SUM(E6:E228)</f>
         <v/>
       </c>
-      <c r="F229" s="14">
+      <c r="F229" s="17">
         <f>SUM(F6:F228)</f>
         <v/>
       </c>
-      <c r="G229" s="14">
+      <c r="G229" s="17">
         <f>SUM(G6:G228)</f>
         <v/>
       </c>
-      <c r="H229" s="14">
+      <c r="H229" s="17">
         <f>SUM(H6:H228)</f>
         <v/>
       </c>
-      <c r="I229" s="14">
+      <c r="I229" s="17">
         <f>SUM(I6:I228)</f>
         <v/>
       </c>
-      <c r="J229" s="14">
+      <c r="J229" s="17">
         <f>SUM(J6:J228)</f>
         <v/>
       </c>
-      <c r="K229" s="14">
+      <c r="K229" s="17">
         <f>SUM(K6:K228)</f>
         <v/>
       </c>
-      <c r="L229" s="14">
+      <c r="L229" s="17">
         <f>SUM(L6:L228)</f>
         <v/>
       </c>
-      <c r="M229" s="14">
+      <c r="M229" s="17">
         <f>SUM(M6:M228)</f>
         <v/>
       </c>
-      <c r="N229" s="14">
+      <c r="N229" s="17">
         <f>SUM(N6:N228)</f>
         <v/>
       </c>
-      <c r="O229" s="14">
+      <c r="O229" s="17">
         <f>SUM(O6:O228)</f>
         <v/>
       </c>
-      <c r="P229" s="14">
+      <c r="P229" s="17">
         <f>SUM(P6:P228)</f>
         <v/>
       </c>
-      <c r="Q229" s="14">
+      <c r="Q229" s="17">
         <f>SUM(Q6:Q228)</f>
         <v/>
       </c>
-      <c r="R229" s="14">
+      <c r="R229" s="17">
         <f>SUM(R6:R228)</f>
         <v/>
       </c>
-      <c r="S229" s="14">
+      <c r="S229" s="17">
         <f>SUM(S6:S228)</f>
         <v/>
       </c>
-      <c r="T229" s="14">
+      <c r="T229" s="17">
         <f>SUM(T6:T228)</f>
         <v/>
       </c>
-      <c r="U229" s="14">
+      <c r="U229" s="17">
         <f>SUM(U6:U228)</f>
         <v/>
       </c>
-      <c r="V229" s="14">
+      <c r="V229" s="17">
         <f>SUM(V6:V228)</f>
         <v/>
       </c>
-      <c r="W229" s="14">
+      <c r="W229" s="17">
         <f>SUM(W6:W228)</f>
         <v/>
       </c>
-      <c r="X229" s="14">
+      <c r="X229" s="17">
         <f>SUM(X6:X228)</f>
         <v/>
       </c>
-      <c r="Y229" s="14">
+      <c r="Y229" s="17">
         <f>SUM(Y6:Y228)</f>
         <v/>
       </c>
-      <c r="Z229" s="14">
+      <c r="Z229" s="17">
         <f>SUM(Z6:Z228)</f>
         <v/>
       </c>
-      <c r="AA229" s="14">
+      <c r="AA229" s="17">
         <f>SUM(AA6:AA228)</f>
         <v/>
       </c>
-      <c r="AB229" s="14">
+      <c r="AB229" s="17">
         <f>SUM(AB6:AB228)</f>
         <v/>
       </c>
-      <c r="AC229" s="14">
+      <c r="AC229" s="17">
         <f>SUM(AC6:AC228)</f>
         <v/>
       </c>
-      <c r="AD229" s="14">
+      <c r="AD229" s="17">
         <f>SUM(AD6:AD228)</f>
         <v/>
       </c>
-      <c r="AE229" s="14">
+      <c r="AE229" s="17">
         <f>SUM(AE6:AE228)</f>
         <v/>
       </c>
-      <c r="AF229" s="14">
+      <c r="AF229" s="17">
         <f>SUM(AF6:AF228)</f>
         <v/>
       </c>
-      <c r="AG229" s="14">
+      <c r="AG229" s="17">
         <f>SUM(AG6:AG228)</f>
         <v/>
       </c>
-      <c r="AH229" s="14">
+      <c r="AH229" s="17">
         <f>SUM(AH6:AH228)</f>
         <v/>
       </c>
-      <c r="AI229" s="14">
+      <c r="AI229" s="17">
         <f>SUM(AI6:AI228)</f>
         <v/>
       </c>
-      <c r="AJ229" s="14">
+      <c r="AJ229" s="17">
         <f>SUM(AJ6:AJ228)</f>
         <v/>
       </c>
-      <c r="AK229" s="14">
+      <c r="AK229" s="17">
         <f>SUM(AK6:AK228)</f>
         <v/>
       </c>
-      <c r="AL229" s="14">
+      <c r="AL229" s="17">
         <f>SUM(AL6:AL228)</f>
         <v/>
       </c>
-      <c r="AM229" s="14">
+      <c r="AM229" s="17">
         <f>SUM(AM6:AM228)</f>
         <v/>
       </c>
-      <c r="AN229" s="14">
+      <c r="AN229" s="17">
         <f>SUM(AN6:AN228)</f>
         <v/>
       </c>
-      <c r="AO229" s="14">
+      <c r="AO229" s="17">
         <f>SUM(AO6:AO228)</f>
         <v/>
       </c>
-      <c r="AP229" s="14">
+      <c r="AP229" s="17">
         <f>SUM(AP6:AP228)</f>
         <v/>
       </c>
-      <c r="AQ229" s="14">
+      <c r="AQ229" s="17">
         <f>SUM(AQ6:AQ228)</f>
         <v/>
       </c>
-      <c r="AR229" s="14">
+      <c r="AR229" s="17">
         <f>SUM(AR6:AR228)</f>
         <v/>
       </c>
-      <c r="AS229" s="14">
+      <c r="AS229" s="17">
         <f>SUM(AS6:AS228)</f>
         <v/>
       </c>
-      <c r="AT229" s="14">
+      <c r="AT229" s="17">
         <f>SUM(AT6:AT228)</f>
         <v/>
       </c>
-      <c r="AU229" s="14">
+      <c r="AU229" s="17">
         <f>SUM(AU6:AU228)</f>
         <v/>
       </c>
-      <c r="AV229" s="14">
+      <c r="AV229" s="17">
         <f>SUM(AV6:AV228)</f>
         <v/>
       </c>
-      <c r="AW229" s="14">
+      <c r="AW229" s="17">
         <f>SUM(AW6:AW228)</f>
         <v/>
       </c>
-      <c r="AX229" s="14">
+      <c r="AX229" s="17">
         <f>SUM(AX6:AX228)</f>
         <v/>
       </c>
-      <c r="AY229" s="14">
+      <c r="AY229" s="17">
         <f>SUM(AY6:AY228)</f>
         <v/>
       </c>
-      <c r="AZ229" s="14">
+      <c r="AZ229" s="17">
         <f>SUM(AZ6:AZ228)</f>
         <v/>
       </c>
-      <c r="BA229" s="14">
+      <c r="BA229" s="17">
         <f>SUM(BA6:BA228)</f>
         <v/>
       </c>
-      <c r="BB229" s="14">
+      <c r="BB229" s="17">
         <f>SUM(BB6:BB228)</f>
         <v/>
       </c>
-      <c r="BC229" s="14">
+      <c r="BC229" s="17">
         <f>SUM(BC6:BC228)</f>
         <v/>
       </c>
-      <c r="BD229" s="14">
+      <c r="BD229" s="17">
         <f>SUM(BD6:BD228)</f>
         <v/>
       </c>
-      <c r="BE229" s="14">
+      <c r="BE229" s="17">
         <f>SUM(BE6:BE228)</f>
         <v/>
       </c>
-      <c r="BF229" s="14">
+      <c r="BF229" s="17">
         <f>SUM(BF6:BF228)</f>
         <v/>
       </c>
-      <c r="BG229" s="14">
+      <c r="BG229" s="17">
         <f>SUM(BG6:BG228)</f>
         <v/>
       </c>
-      <c r="BH229" s="14">
+      <c r="BH229" s="17">
         <f>SUM(BH6:BH228)</f>
         <v/>
       </c>
-      <c r="BI229" s="14">
+      <c r="BI229" s="17">
         <f>SUM(BI6:BI228)</f>
         <v/>
       </c>
-      <c r="BJ229" s="14">
+      <c r="BJ229" s="17">
         <f>SUM(BJ6:BJ228)</f>
         <v/>
       </c>
-      <c r="BK229" s="14">
+      <c r="BK229" s="17">
         <f>SUM(BK6:BK228)</f>
         <v/>
       </c>
-      <c r="BL229" s="14">
+      <c r="BL229" s="17">
         <f>SUM(BL6:BL228)</f>
         <v/>
       </c>
-      <c r="BM229" s="14">
+      <c r="BM229" s="17">
         <f>SUM(BM6:BM228)</f>
         <v/>
       </c>
-      <c r="BN229" s="14">
+      <c r="BN229" s="17">
         <f>SUM(BN6:BN228)</f>
         <v/>
       </c>
-      <c r="BO229" s="14">
+      <c r="BO229" s="17">
         <f>SUM(BO6:BO228)</f>
         <v/>
       </c>
-      <c r="BP229" s="14">
+      <c r="BP229" s="17">
         <f>SUM(BP6:BP228)</f>
         <v/>
       </c>
-      <c r="BQ229" s="14">
+      <c r="BQ229" s="17">
         <f>SUM(BQ6:BQ228)</f>
         <v/>
       </c>
-      <c r="BR229" s="14">
+      <c r="BR229" s="17">
         <f>SUM(BR6:BR228)</f>
         <v/>
       </c>
-      <c r="BS229" s="14">
+      <c r="BS229" s="17">
         <f>SUM(BS6:BS228)</f>
         <v/>
       </c>
-      <c r="BT229" s="14">
+      <c r="BT229" s="17">
         <f>SUM(BT6:BT228)</f>
         <v/>
       </c>
-      <c r="BU229" s="14">
+      <c r="BU229" s="17">
         <f>SUM(BU6:BU228)</f>
         <v/>
       </c>
-      <c r="BV229" s="14">
+      <c r="BV229" s="17">
         <f>SUM(BV6:BV228)</f>
         <v/>
       </c>
-      <c r="BW229" s="14">
+      <c r="BW229" s="17">
         <f>SUM(BW6:BW228)</f>
         <v/>
       </c>
-      <c r="BX229" s="14">
+      <c r="BX229" s="17">
         <f>SUM(BX6:BX228)</f>
         <v/>
       </c>
-      <c r="BY229" s="14">
+      <c r="BY229" s="17">
         <f>SUM(BY6:BY228)</f>
         <v/>
       </c>
-      <c r="BZ229" s="14">
+      <c r="BZ229" s="17">
         <f>SUM(BZ6:BZ228)</f>
         <v/>
       </c>
-      <c r="CA229" s="14">
+      <c r="CA229" s="17">
         <f>SUM(CA6:CA228)</f>
         <v/>
       </c>
-      <c r="CB229" s="14">
+      <c r="CB229" s="17">
         <f>SUM(CB6:CB228)</f>
         <v/>
       </c>
-      <c r="CC229" s="14">
+      <c r="CC229" s="17">
         <f>SUM(CC6:CC228)</f>
         <v/>
       </c>
-      <c r="CD229" s="14">
+      <c r="CD229" s="17">
         <f>SUM(CD6:CD228)</f>
         <v/>
       </c>
-      <c r="CE229" s="14">
+      <c r="CE229" s="17">
         <f>SUM(CE6:CE228)</f>
         <v/>
       </c>
-      <c r="CF229" s="14">
+      <c r="CF229" s="17">
         <f>SUM(CF6:CF228)</f>
         <v/>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="9" t="inlineStr">
+      <c r="A230" s="18" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B230" s="10" t="inlineStr"/>
-      <c r="C230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB230" s="10" t="n">
+      <c r="C230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB230" s="17" t="n">
         <v>268</v>
       </c>
-      <c r="CC230" s="10" t="n">
+      <c r="CC230" s="17" t="n">
         <v>57</v>
       </c>
-      <c r="CD230" s="10" t="n">
+      <c r="CD230" s="17" t="n">
         <v>325</v>
       </c>
-      <c r="CE230" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF230" s="10" t="n">
+      <c r="CE230" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF230" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="11" t="inlineStr">
+      <c r="A231" s="19" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B231" s="12" t="inlineStr"/>
-      <c r="C231" s="12">
+      <c r="B231" s="20" t="inlineStr"/>
+      <c r="C231" s="21">
         <f>C229+C230</f>
         <v/>
       </c>
-      <c r="D231" s="12">
+      <c r="D231" s="21">
         <f>D229+D230</f>
         <v/>
       </c>
-      <c r="E231" s="12">
+      <c r="E231" s="21">
         <f>E229+E230</f>
         <v/>
       </c>
-      <c r="F231" s="12">
+      <c r="F231" s="21">
         <f>F229+F230</f>
         <v/>
       </c>
-      <c r="G231" s="12">
+      <c r="G231" s="21">
         <f>G229+G230</f>
         <v/>
       </c>
-      <c r="H231" s="12">
+      <c r="H231" s="21">
         <f>H229+H230</f>
         <v/>
       </c>
-      <c r="I231" s="12">
+      <c r="I231" s="21">
         <f>I229+I230</f>
         <v/>
       </c>
-      <c r="J231" s="12">
+      <c r="J231" s="21">
         <f>J229+J230</f>
         <v/>
       </c>
-      <c r="K231" s="12">
+      <c r="K231" s="21">
         <f>K229+K230</f>
         <v/>
       </c>
-      <c r="L231" s="12">
+      <c r="L231" s="21">
         <f>L229+L230</f>
         <v/>
       </c>
-      <c r="M231" s="12">
+      <c r="M231" s="21">
         <f>M229+M230</f>
         <v/>
       </c>
-      <c r="N231" s="12">
+      <c r="N231" s="21">
         <f>N229+N230</f>
         <v/>
       </c>
-      <c r="O231" s="12">
+      <c r="O231" s="21">
         <f>O229+O230</f>
         <v/>
       </c>
-      <c r="P231" s="12">
+      <c r="P231" s="21">
         <f>P229+P230</f>
         <v/>
       </c>
-      <c r="Q231" s="12">
+      <c r="Q231" s="21">
         <f>Q229+Q230</f>
         <v/>
       </c>
-      <c r="R231" s="12">
+      <c r="R231" s="21">
         <f>R229+R230</f>
         <v/>
       </c>
-      <c r="S231" s="12">
+      <c r="S231" s="21">
         <f>S229+S230</f>
         <v/>
       </c>
-      <c r="T231" s="12">
+      <c r="T231" s="21">
         <f>T229+T230</f>
         <v/>
       </c>
-      <c r="U231" s="12">
+      <c r="U231" s="21">
         <f>U229+U230</f>
         <v/>
       </c>
-      <c r="V231" s="12">
+      <c r="V231" s="21">
         <f>V229+V230</f>
         <v/>
       </c>
-      <c r="W231" s="12">
+      <c r="W231" s="21">
         <f>W229+W230</f>
         <v/>
       </c>
-      <c r="X231" s="12">
+      <c r="X231" s="21">
         <f>X229+X230</f>
         <v/>
       </c>
-      <c r="Y231" s="12">
+      <c r="Y231" s="21">
         <f>Y229+Y230</f>
         <v/>
       </c>
-      <c r="Z231" s="12">
+      <c r="Z231" s="21">
         <f>Z229+Z230</f>
         <v/>
       </c>
-      <c r="AA231" s="12">
+      <c r="AA231" s="21">
         <f>AA229+AA230</f>
         <v/>
       </c>
-      <c r="AB231" s="12">
+      <c r="AB231" s="21">
         <f>AB229+AB230</f>
         <v/>
       </c>
-      <c r="AC231" s="12">
+      <c r="AC231" s="21">
         <f>AC229+AC230</f>
         <v/>
       </c>
-      <c r="AD231" s="12">
+      <c r="AD231" s="21">
         <f>AD229+AD230</f>
         <v/>
       </c>
-      <c r="AE231" s="12">
+      <c r="AE231" s="21">
         <f>AE229+AE230</f>
         <v/>
       </c>
-      <c r="AF231" s="12">
+      <c r="AF231" s="21">
         <f>AF229+AF230</f>
         <v/>
       </c>
-      <c r="AG231" s="12">
+      <c r="AG231" s="21">
         <f>AG229+AG230</f>
         <v/>
       </c>
-      <c r="AH231" s="12">
+      <c r="AH231" s="21">
         <f>AH229+AH230</f>
         <v/>
       </c>
-      <c r="AI231" s="12">
+      <c r="AI231" s="21">
         <f>AI229+AI230</f>
         <v/>
       </c>
-      <c r="AJ231" s="12">
+      <c r="AJ231" s="21">
         <f>AJ229+AJ230</f>
         <v/>
       </c>
-      <c r="AK231" s="12">
+      <c r="AK231" s="21">
         <f>AK229+AK230</f>
         <v/>
       </c>
-      <c r="AL231" s="12">
+      <c r="AL231" s="21">
         <f>AL229+AL230</f>
         <v/>
       </c>
-      <c r="AM231" s="12">
+      <c r="AM231" s="21">
         <f>AM229+AM230</f>
         <v/>
       </c>
-      <c r="AN231" s="12">
+      <c r="AN231" s="21">
         <f>AN229+AN230</f>
         <v/>
       </c>
-      <c r="AO231" s="12">
+      <c r="AO231" s="21">
         <f>AO229+AO230</f>
         <v/>
       </c>
-      <c r="AP231" s="12">
+      <c r="AP231" s="21">
         <f>AP229+AP230</f>
         <v/>
       </c>
-      <c r="AQ231" s="12">
+      <c r="AQ231" s="21">
         <f>AQ229+AQ230</f>
         <v/>
       </c>
-      <c r="AR231" s="12">
+      <c r="AR231" s="21">
         <f>AR229+AR230</f>
         <v/>
       </c>
-      <c r="AS231" s="12">
+      <c r="AS231" s="21">
         <f>AS229+AS230</f>
         <v/>
       </c>
-      <c r="AT231" s="12">
+      <c r="AT231" s="21">
         <f>AT229+AT230</f>
         <v/>
       </c>
-      <c r="AU231" s="12">
+      <c r="AU231" s="21">
         <f>AU229+AU230</f>
         <v/>
       </c>
-      <c r="AV231" s="12">
+      <c r="AV231" s="21">
         <f>AV229+AV230</f>
         <v/>
       </c>
-      <c r="AW231" s="12">
+      <c r="AW231" s="21">
         <f>AW229+AW230</f>
         <v/>
       </c>
-      <c r="AX231" s="12">
+      <c r="AX231" s="21">
         <f>AX229+AX230</f>
         <v/>
       </c>
-      <c r="AY231" s="12">
+      <c r="AY231" s="21">
         <f>AY229+AY230</f>
         <v/>
       </c>
-      <c r="AZ231" s="12">
+      <c r="AZ231" s="21">
         <f>AZ229+AZ230</f>
         <v/>
       </c>
-      <c r="BA231" s="12">
+      <c r="BA231" s="21">
         <f>BA229+BA230</f>
         <v/>
       </c>
-      <c r="BB231" s="12">
+      <c r="BB231" s="21">
         <f>BB229+BB230</f>
         <v/>
       </c>
-      <c r="BC231" s="12">
+      <c r="BC231" s="21">
         <f>BC229+BC230</f>
         <v/>
       </c>
-      <c r="BD231" s="12">
+      <c r="BD231" s="21">
         <f>BD229+BD230</f>
         <v/>
       </c>
-      <c r="BE231" s="12">
+      <c r="BE231" s="21">
         <f>BE229+BE230</f>
         <v/>
       </c>
-      <c r="BF231" s="12">
+      <c r="BF231" s="21">
         <f>BF229+BF230</f>
         <v/>
       </c>
-      <c r="BG231" s="12">
+      <c r="BG231" s="21">
         <f>BG229+BG230</f>
         <v/>
       </c>
-      <c r="BH231" s="12">
+      <c r="BH231" s="21">
         <f>BH229+BH230</f>
         <v/>
       </c>
-      <c r="BI231" s="12">
+      <c r="BI231" s="21">
         <f>BI229+BI230</f>
         <v/>
       </c>
-      <c r="BJ231" s="12">
+      <c r="BJ231" s="21">
         <f>BJ229+BJ230</f>
         <v/>
       </c>
-      <c r="BK231" s="12">
+      <c r="BK231" s="21">
         <f>BK229+BK230</f>
         <v/>
       </c>
-      <c r="BL231" s="12">
+      <c r="BL231" s="21">
         <f>BL229+BL230</f>
         <v/>
       </c>
-      <c r="BM231" s="12">
+      <c r="BM231" s="21">
         <f>BM229+BM230</f>
         <v/>
       </c>
-      <c r="BN231" s="12">
+      <c r="BN231" s="21">
         <f>BN229+BN230</f>
         <v/>
       </c>
-      <c r="BO231" s="12">
+      <c r="BO231" s="21">
         <f>BO229+BO230</f>
         <v/>
       </c>
-      <c r="BP231" s="12">
+      <c r="BP231" s="21">
         <f>BP229+BP230</f>
         <v/>
       </c>
-      <c r="BQ231" s="12">
+      <c r="BQ231" s="21">
         <f>BQ229+BQ230</f>
         <v/>
       </c>
-      <c r="BR231" s="12">
+      <c r="BR231" s="21">
         <f>BR229+BR230</f>
         <v/>
       </c>
-      <c r="BS231" s="12">
+      <c r="BS231" s="21">
         <f>BS229+BS230</f>
         <v/>
       </c>
-      <c r="BT231" s="12">
+      <c r="BT231" s="21">
         <f>BT229+BT230</f>
         <v/>
       </c>
-      <c r="BU231" s="12">
+      <c r="BU231" s="21">
         <f>BU229+BU230</f>
         <v/>
       </c>
-      <c r="BV231" s="12">
+      <c r="BV231" s="21">
         <f>BV229+BV230</f>
         <v/>
       </c>
-      <c r="BW231" s="12">
+      <c r="BW231" s="21">
         <f>BW229+BW230</f>
         <v/>
       </c>
-      <c r="BX231" s="12">
+      <c r="BX231" s="21">
         <f>BX229+BX230</f>
         <v/>
       </c>
-      <c r="BY231" s="12">
+      <c r="BY231" s="21">
         <f>BY229+BY230</f>
         <v/>
       </c>
-      <c r="BZ231" s="12">
+      <c r="BZ231" s="21">
         <f>BZ229+BZ230</f>
         <v/>
       </c>
-      <c r="CA231" s="12">
+      <c r="CA231" s="21">
         <f>CA229+CA230</f>
         <v/>
       </c>
-      <c r="CB231" s="12">
+      <c r="CB231" s="21">
         <f>CB229+CB230</f>
         <v/>
       </c>
-      <c r="CC231" s="12">
+      <c r="CC231" s="21">
         <f>CC229+CC230</f>
         <v/>
       </c>
-      <c r="CD231" s="12">
+      <c r="CD231" s="21">
         <f>CD229+CD230</f>
         <v/>
       </c>
-      <c r="CE231" s="12">
+      <c r="CE231" s="21">
         <f>CE229+CE230</f>
         <v/>
       </c>
-      <c r="CF231" s="12">
+      <c r="CF231" s="21">
         <f>CF229+CF230</f>
         <v/>
       </c>

--- a/AC_2010Bye/AC_029_Sircilla.xlsx
+++ b/AC_2010Bye/AC_029_Sircilla.xlsx
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="CF6" s="4" t="n">
-        <v>-48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="CF7" s="4" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1876,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="CF8" s="4" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2132,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="CF9" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2388,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="CF10" s="4" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2644,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="CF11" s="4" t="n">
-        <v>-23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2900,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="CF12" s="4" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3156,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="CF13" s="4" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3413,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="CF14" s="4" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3669,7 +3669,7 @@
         <v>0</v>
       </c>
       <c r="CF15" s="4" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3925,7 +3925,7 @@
         <v>0</v>
       </c>
       <c r="CF16" s="4" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="CF17" s="4" t="n">
-        <v>-35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -4437,7 +4437,7 @@
         <v>0</v>
       </c>
       <c r="CF18" s="4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -4693,7 +4693,7 @@
         <v>0</v>
       </c>
       <c r="CF19" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -4949,7 +4949,7 @@
         <v>0</v>
       </c>
       <c r="CF20" s="4" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="CF21" s="4" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -5461,7 +5461,7 @@
         <v>0</v>
       </c>
       <c r="CF22" s="4" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -5717,7 +5717,7 @@
         <v>0</v>
       </c>
       <c r="CF23" s="4" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -5973,7 +5973,7 @@
         <v>0</v>
       </c>
       <c r="CF24" s="4" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -6229,7 +6229,7 @@
         <v>0</v>
       </c>
       <c r="CF25" s="4" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -6485,7 +6485,7 @@
         <v>0</v>
       </c>
       <c r="CF26" s="4" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -6997,7 +6997,7 @@
         <v>0</v>
       </c>
       <c r="CF28" s="4" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -7253,7 +7253,7 @@
         <v>0</v>
       </c>
       <c r="CF29" s="4" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -7509,7 +7509,7 @@
         <v>0</v>
       </c>
       <c r="CF30" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -7765,7 +7765,7 @@
         <v>0</v>
       </c>
       <c r="CF31" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -8021,7 +8021,7 @@
         <v>0</v>
       </c>
       <c r="CF32" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -8277,7 +8277,7 @@
         <v>0</v>
       </c>
       <c r="CF33" s="4" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -8533,7 +8533,7 @@
         <v>0</v>
       </c>
       <c r="CF34" s="4" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -8789,7 +8789,7 @@
         <v>0</v>
       </c>
       <c r="CF35" s="4" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -9045,7 +9045,7 @@
         <v>0</v>
       </c>
       <c r="CF36" s="4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -9301,7 +9301,7 @@
         <v>0</v>
       </c>
       <c r="CF37" s="4" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -9557,7 +9557,7 @@
         <v>0</v>
       </c>
       <c r="CF38" s="4" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -9813,7 +9813,7 @@
         <v>0</v>
       </c>
       <c r="CF39" s="4" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -10069,7 +10069,7 @@
         <v>0</v>
       </c>
       <c r="CF40" s="4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -10325,7 +10325,7 @@
         <v>0</v>
       </c>
       <c r="CF41" s="4" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -10581,7 +10581,7 @@
         <v>0</v>
       </c>
       <c r="CF42" s="4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -11093,7 +11093,7 @@
         <v>0</v>
       </c>
       <c r="CF44" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -11349,7 +11349,7 @@
         <v>0</v>
       </c>
       <c r="CF45" s="4" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -11605,7 +11605,7 @@
         <v>0</v>
       </c>
       <c r="CF46" s="4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -11861,7 +11861,7 @@
         <v>0</v>
       </c>
       <c r="CF47" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -12117,7 +12117,7 @@
         <v>0</v>
       </c>
       <c r="CF48" s="4" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -12373,7 +12373,7 @@
         <v>0</v>
       </c>
       <c r="CF49" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -12629,7 +12629,7 @@
         <v>0</v>
       </c>
       <c r="CF50" s="4" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -12885,7 +12885,7 @@
         <v>0</v>
       </c>
       <c r="CF51" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -13141,7 +13141,7 @@
         <v>0</v>
       </c>
       <c r="CF52" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -13397,7 +13397,7 @@
         <v>0</v>
       </c>
       <c r="CF53" s="4" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -13653,7 +13653,7 @@
         <v>0</v>
       </c>
       <c r="CF54" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -13909,7 +13909,7 @@
         <v>0</v>
       </c>
       <c r="CF55" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -14165,7 +14165,7 @@
         <v>0</v>
       </c>
       <c r="CF56" s="4" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -14421,7 +14421,7 @@
         <v>0</v>
       </c>
       <c r="CF57" s="4" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -14677,7 +14677,7 @@
         <v>0</v>
       </c>
       <c r="CF58" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -14933,7 +14933,7 @@
         <v>0</v>
       </c>
       <c r="CF59" s="4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -15189,7 +15189,7 @@
         <v>0</v>
       </c>
       <c r="CF60" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -15445,7 +15445,7 @@
         <v>0</v>
       </c>
       <c r="CF61" s="4" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -15701,7 +15701,7 @@
         <v>0</v>
       </c>
       <c r="CF62" s="4" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -16213,7 +16213,7 @@
         <v>0</v>
       </c>
       <c r="CF64" s="4" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -16469,7 +16469,7 @@
         <v>0</v>
       </c>
       <c r="CF65" s="4" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -16725,7 +16725,7 @@
         <v>0</v>
       </c>
       <c r="CF66" s="4" t="n">
-        <v>-23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -16981,7 +16981,7 @@
         <v>0</v>
       </c>
       <c r="CF67" s="4" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -17237,7 +17237,7 @@
         <v>0</v>
       </c>
       <c r="CF68" s="4" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -17493,7 +17493,7 @@
         <v>0</v>
       </c>
       <c r="CF69" s="4" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -17749,7 +17749,7 @@
         <v>0</v>
       </c>
       <c r="CF70" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -18005,7 +18005,7 @@
         <v>0</v>
       </c>
       <c r="CF71" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -18261,7 +18261,7 @@
         <v>0</v>
       </c>
       <c r="CF72" s="4" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -18517,7 +18517,7 @@
         <v>0</v>
       </c>
       <c r="CF73" s="4" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -18773,7 +18773,7 @@
         <v>0</v>
       </c>
       <c r="CF74" s="4" t="n">
-        <v>-28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -19029,7 +19029,7 @@
         <v>0</v>
       </c>
       <c r="CF75" s="4" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -19285,7 +19285,7 @@
         <v>0</v>
       </c>
       <c r="CF76" s="4" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -19541,7 +19541,7 @@
         <v>0</v>
       </c>
       <c r="CF77" s="4" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -19797,7 +19797,7 @@
         <v>0</v>
       </c>
       <c r="CF78" s="4" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -20053,7 +20053,7 @@
         <v>0</v>
       </c>
       <c r="CF79" s="4" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -20309,7 +20309,7 @@
         <v>0</v>
       </c>
       <c r="CF80" s="4" t="n">
-        <v>-27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -20565,7 +20565,7 @@
         <v>0</v>
       </c>
       <c r="CF81" s="4" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -20821,7 +20821,7 @@
         <v>0</v>
       </c>
       <c r="CF82" s="4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -21077,7 +21077,7 @@
         <v>0</v>
       </c>
       <c r="CF83" s="4" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -21589,7 +21589,7 @@
         <v>0</v>
       </c>
       <c r="CF85" s="4" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -22101,7 +22101,7 @@
         <v>0</v>
       </c>
       <c r="CF87" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -22357,7 +22357,7 @@
         <v>0</v>
       </c>
       <c r="CF88" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -22613,7 +22613,7 @@
         <v>0</v>
       </c>
       <c r="CF89" s="4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -22869,7 +22869,7 @@
         <v>0</v>
       </c>
       <c r="CF90" s="4" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -23125,7 +23125,7 @@
         <v>0</v>
       </c>
       <c r="CF91" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -23381,7 +23381,7 @@
         <v>0</v>
       </c>
       <c r="CF92" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -24405,7 +24405,7 @@
         <v>0</v>
       </c>
       <c r="CF96" s="4" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -24917,7 +24917,7 @@
         <v>0</v>
       </c>
       <c r="CF98" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -25173,7 +25173,7 @@
         <v>0</v>
       </c>
       <c r="CF99" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -25941,7 +25941,7 @@
         <v>0</v>
       </c>
       <c r="CF102" s="4" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -26197,7 +26197,7 @@
         <v>0</v>
       </c>
       <c r="CF103" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -26453,7 +26453,7 @@
         <v>0</v>
       </c>
       <c r="CF104" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -26709,7 +26709,7 @@
         <v>0</v>
       </c>
       <c r="CF105" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -26965,7 +26965,7 @@
         <v>0</v>
       </c>
       <c r="CF106" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -27477,7 +27477,7 @@
         <v>0</v>
       </c>
       <c r="CF108" s="4" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -27733,7 +27733,7 @@
         <v>0</v>
       </c>
       <c r="CF109" s="4" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -27989,7 +27989,7 @@
         <v>0</v>
       </c>
       <c r="CF110" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -28501,7 +28501,7 @@
         <v>0</v>
       </c>
       <c r="CF112" s="4" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -28757,7 +28757,7 @@
         <v>0</v>
       </c>
       <c r="CF113" s="4" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -29525,7 +29525,7 @@
         <v>0</v>
       </c>
       <c r="CF116" s="4" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -29781,7 +29781,7 @@
         <v>0</v>
       </c>
       <c r="CF117" s="4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -30805,7 +30805,7 @@
         <v>0</v>
       </c>
       <c r="CF121" s="4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -31573,7 +31573,7 @@
         <v>0</v>
       </c>
       <c r="CF124" s="4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -31829,7 +31829,7 @@
         <v>0</v>
       </c>
       <c r="CF125" s="4" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -32085,7 +32085,7 @@
         <v>0</v>
       </c>
       <c r="CF126" s="4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -32341,7 +32341,7 @@
         <v>0</v>
       </c>
       <c r="CF127" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -32597,7 +32597,7 @@
         <v>0</v>
       </c>
       <c r="CF128" s="4" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -32853,7 +32853,7 @@
         <v>0</v>
       </c>
       <c r="CF129" s="4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -33109,7 +33109,7 @@
         <v>0</v>
       </c>
       <c r="CF130" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -33621,7 +33621,7 @@
         <v>0</v>
       </c>
       <c r="CF132" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -33877,7 +33877,7 @@
         <v>0</v>
       </c>
       <c r="CF133" s="4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -34133,7 +34133,7 @@
         <v>0</v>
       </c>
       <c r="CF134" s="4" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -34389,7 +34389,7 @@
         <v>0</v>
       </c>
       <c r="CF135" s="4" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -34645,7 +34645,7 @@
         <v>0</v>
       </c>
       <c r="CF136" s="4" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -34901,7 +34901,7 @@
         <v>0</v>
       </c>
       <c r="CF137" s="4" t="n">
-        <v>-32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -35157,7 +35157,7 @@
         <v>0</v>
       </c>
       <c r="CF138" s="4" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -35413,7 +35413,7 @@
         <v>0</v>
       </c>
       <c r="CF139" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -35669,7 +35669,7 @@
         <v>0</v>
       </c>
       <c r="CF140" s="4" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -35925,7 +35925,7 @@
         <v>0</v>
       </c>
       <c r="CF141" s="4" t="n">
-        <v>-42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -36181,7 +36181,7 @@
         <v>0</v>
       </c>
       <c r="CF142" s="4" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -36437,7 +36437,7 @@
         <v>0</v>
       </c>
       <c r="CF143" s="4" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -36693,7 +36693,7 @@
         <v>0</v>
       </c>
       <c r="CF144" s="4" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -36949,7 +36949,7 @@
         <v>0</v>
       </c>
       <c r="CF145" s="4" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -37205,7 +37205,7 @@
         <v>0</v>
       </c>
       <c r="CF146" s="4" t="n">
-        <v>-33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -37461,7 +37461,7 @@
         <v>0</v>
       </c>
       <c r="CF147" s="4" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -37717,7 +37717,7 @@
         <v>0</v>
       </c>
       <c r="CF148" s="4" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -37973,7 +37973,7 @@
         <v>0</v>
       </c>
       <c r="CF149" s="4" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -38229,7 +38229,7 @@
         <v>0</v>
       </c>
       <c r="CF150" s="4" t="n">
-        <v>-23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -38485,7 +38485,7 @@
         <v>0</v>
       </c>
       <c r="CF151" s="4" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -38741,7 +38741,7 @@
         <v>0</v>
       </c>
       <c r="CF152" s="4" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -38997,7 +38997,7 @@
         <v>0</v>
       </c>
       <c r="CF153" s="4" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -39253,7 +39253,7 @@
         <v>0</v>
       </c>
       <c r="CF154" s="4" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -39509,7 +39509,7 @@
         <v>0</v>
       </c>
       <c r="CF155" s="4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -39765,7 +39765,7 @@
         <v>0</v>
       </c>
       <c r="CF156" s="4" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -40021,7 +40021,7 @@
         <v>0</v>
       </c>
       <c r="CF157" s="4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -40277,7 +40277,7 @@
         <v>0</v>
       </c>
       <c r="CF158" s="4" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -40533,7 +40533,7 @@
         <v>0</v>
       </c>
       <c r="CF159" s="4" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -40789,7 +40789,7 @@
         <v>0</v>
       </c>
       <c r="CF160" s="4" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -41045,7 +41045,7 @@
         <v>0</v>
       </c>
       <c r="CF161" s="4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -41301,7 +41301,7 @@
         <v>0</v>
       </c>
       <c r="CF162" s="4" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -41557,7 +41557,7 @@
         <v>0</v>
       </c>
       <c r="CF163" s="4" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -41813,7 +41813,7 @@
         <v>0</v>
       </c>
       <c r="CF164" s="4" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -42069,7 +42069,7 @@
         <v>0</v>
       </c>
       <c r="CF165" s="4" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -42325,7 +42325,7 @@
         <v>0</v>
       </c>
       <c r="CF166" s="4" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -42581,7 +42581,7 @@
         <v>0</v>
       </c>
       <c r="CF167" s="4" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -42837,7 +42837,7 @@
         <v>0</v>
       </c>
       <c r="CF168" s="4" t="n">
-        <v>-23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -43093,7 +43093,7 @@
         <v>0</v>
       </c>
       <c r="CF169" s="4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -43349,7 +43349,7 @@
         <v>0</v>
       </c>
       <c r="CF170" s="4" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -43605,7 +43605,7 @@
         <v>0</v>
       </c>
       <c r="CF171" s="4" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -43861,7 +43861,7 @@
         <v>0</v>
       </c>
       <c r="CF172" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -44117,7 +44117,7 @@
         <v>0</v>
       </c>
       <c r="CF173" s="4" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -44373,7 +44373,7 @@
         <v>0</v>
       </c>
       <c r="CF174" s="4" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -44629,7 +44629,7 @@
         <v>0</v>
       </c>
       <c r="CF175" s="4" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -44885,7 +44885,7 @@
         <v>0</v>
       </c>
       <c r="CF176" s="4" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -45141,7 +45141,7 @@
         <v>0</v>
       </c>
       <c r="CF177" s="4" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -45397,7 +45397,7 @@
         <v>0</v>
       </c>
       <c r="CF178" s="4" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -45653,7 +45653,7 @@
         <v>0</v>
       </c>
       <c r="CF179" s="4" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -45909,7 +45909,7 @@
         <v>0</v>
       </c>
       <c r="CF180" s="4" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -46165,7 +46165,7 @@
         <v>0</v>
       </c>
       <c r="CF181" s="4" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -46421,7 +46421,7 @@
         <v>0</v>
       </c>
       <c r="CF182" s="4" t="n">
-        <v>-23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -46677,7 +46677,7 @@
         <v>0</v>
       </c>
       <c r="CF183" s="4" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -46933,7 +46933,7 @@
         <v>0</v>
       </c>
       <c r="CF184" s="4" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -47189,7 +47189,7 @@
         <v>0</v>
       </c>
       <c r="CF185" s="4" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -47445,7 +47445,7 @@
         <v>0</v>
       </c>
       <c r="CF186" s="4" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -47701,7 +47701,7 @@
         <v>0</v>
       </c>
       <c r="CF187" s="4" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -47957,7 +47957,7 @@
         <v>0</v>
       </c>
       <c r="CF188" s="4" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -48213,7 +48213,7 @@
         <v>0</v>
       </c>
       <c r="CF189" s="4" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -48470,7 +48470,7 @@
         <v>0</v>
       </c>
       <c r="CF190" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -48982,7 +48982,7 @@
         <v>0</v>
       </c>
       <c r="CF192" s="4" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -49238,7 +49238,7 @@
         <v>0</v>
       </c>
       <c r="CF193" s="4" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -49494,7 +49494,7 @@
         <v>0</v>
       </c>
       <c r="CF194" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -49750,7 +49750,7 @@
         <v>0</v>
       </c>
       <c r="CF195" s="4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -50006,7 +50006,7 @@
         <v>0</v>
       </c>
       <c r="CF196" s="4" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -50262,7 +50262,7 @@
         <v>0</v>
       </c>
       <c r="CF197" s="4" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -50518,7 +50518,7 @@
         <v>0</v>
       </c>
       <c r="CF198" s="4" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -50774,7 +50774,7 @@
         <v>0</v>
       </c>
       <c r="CF199" s="4" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -51030,7 +51030,7 @@
         <v>0</v>
       </c>
       <c r="CF200" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -51286,7 +51286,7 @@
         <v>0</v>
       </c>
       <c r="CF201" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -51542,7 +51542,7 @@
         <v>0</v>
       </c>
       <c r="CF202" s="4" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -51798,7 +51798,7 @@
         <v>0</v>
       </c>
       <c r="CF203" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -52054,7 +52054,7 @@
         <v>0</v>
       </c>
       <c r="CF204" s="4" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -52310,7 +52310,7 @@
         <v>0</v>
       </c>
       <c r="CF205" s="4" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -52566,7 +52566,7 @@
         <v>0</v>
       </c>
       <c r="CF206" s="4" t="n">
-        <v>-23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -52822,7 +52822,7 @@
         <v>0</v>
       </c>
       <c r="CF207" s="4" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -53078,7 +53078,7 @@
         <v>0</v>
       </c>
       <c r="CF208" s="4" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -53334,7 +53334,7 @@
         <v>0</v>
       </c>
       <c r="CF209" s="4" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -53591,7 +53591,7 @@
         <v>0</v>
       </c>
       <c r="CF210" s="4" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -53847,7 +53847,7 @@
         <v>0</v>
       </c>
       <c r="CF211" s="4" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -54103,7 +54103,7 @@
         <v>0</v>
       </c>
       <c r="CF212" s="4" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -54360,7 +54360,7 @@
         <v>0</v>
       </c>
       <c r="CF213" s="4" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -54616,7 +54616,7 @@
         <v>0</v>
       </c>
       <c r="CF214" s="4" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -54872,7 +54872,7 @@
         <v>0</v>
       </c>
       <c r="CF215" s="4" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -55128,7 +55128,7 @@
         <v>0</v>
       </c>
       <c r="CF216" s="4" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -55384,7 +55384,7 @@
         <v>0</v>
       </c>
       <c r="CF217" s="4" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -55640,7 +55640,7 @@
         <v>0</v>
       </c>
       <c r="CF218" s="4" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -55896,7 +55896,7 @@
         <v>0</v>
       </c>
       <c r="CF219" s="4" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -56152,7 +56152,7 @@
         <v>0</v>
       </c>
       <c r="CF220" s="4" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -56408,7 +56408,7 @@
         <v>0</v>
       </c>
       <c r="CF221" s="4" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -56664,7 +56664,7 @@
         <v>0</v>
       </c>
       <c r="CF222" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -56920,7 +56920,7 @@
         <v>0</v>
       </c>
       <c r="CF223" s="4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -57176,7 +57176,7 @@
         <v>0</v>
       </c>
       <c r="CF224" s="4" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -57432,7 +57432,7 @@
         <v>0</v>
       </c>
       <c r="CF225" s="4" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -57688,7 +57688,7 @@
         <v>0</v>
       </c>
       <c r="CF226" s="4" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -57944,7 +57944,7 @@
         <v>0</v>
       </c>
       <c r="CF227" s="4" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -58200,7 +58200,7 @@
         <v>0</v>
       </c>
       <c r="CF228" s="4" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
